--- a/src/attributions/attributions_saliency_traj_495.xlsx
+++ b/src/attributions/attributions_saliency_traj_495.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GG3"/>
+  <dimension ref="A1:GG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,1139 +999,7967 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2.798309196805349e-06</v>
+        <v>0.009631939232349396</v>
       </c>
       <c r="B2" t="n">
-        <v>6.857823609607294e-05</v>
+        <v>0.06964477151632309</v>
       </c>
       <c r="C2" t="n">
-        <v>1.033773878589272e-05</v>
+        <v>0.1384047120809555</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0001113996186177246</v>
+        <v>0.210975855588913</v>
       </c>
       <c r="E2" t="n">
-        <v>1.271485052711796e-05</v>
+        <v>0.1193479597568512</v>
       </c>
       <c r="F2" t="n">
-        <v>1.699950189504307e-05</v>
+        <v>0.01200867351144552</v>
       </c>
       <c r="G2" t="n">
-        <v>2.013372977671679e-05</v>
+        <v>0.01784844137728214</v>
       </c>
       <c r="H2" t="n">
-        <v>1.911777144414373e-05</v>
+        <v>0.002963840961456299</v>
       </c>
       <c r="I2" t="n">
-        <v>1.362473994959146e-06</v>
+        <v>0.01024626195430756</v>
       </c>
       <c r="J2" t="n">
-        <v>1.554690061311703e-05</v>
+        <v>0.03081616014242172</v>
       </c>
       <c r="K2" t="n">
-        <v>6.771647167624906e-05</v>
+        <v>0.06430201977491379</v>
       </c>
       <c r="L2" t="n">
-        <v>1.373544819216477e-06</v>
+        <v>0.110060527920723</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0001052890656865202</v>
+        <v>0.1659729480743408</v>
       </c>
       <c r="N2" t="n">
-        <v>6.001838301017415e-06</v>
+        <v>0.1250543147325516</v>
       </c>
       <c r="O2" t="n">
-        <v>6.059832958271727e-05</v>
+        <v>0.01378954388201237</v>
       </c>
       <c r="P2" t="n">
-        <v>1.232252543559298e-05</v>
+        <v>0.01750452443957329</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.258737342548557e-05</v>
+        <v>0.02924436330795288</v>
       </c>
       <c r="R2" t="n">
-        <v>3.159287734888494e-05</v>
+        <v>0.02679585665464401</v>
       </c>
       <c r="S2" t="n">
-        <v>1.762691317708232e-05</v>
+        <v>0.03605473041534424</v>
       </c>
       <c r="T2" t="n">
-        <v>2.235352076240815e-05</v>
+        <v>0.04091529548168182</v>
       </c>
       <c r="U2" t="n">
-        <v>5.090327249490656e-06</v>
+        <v>0.02254042960703373</v>
       </c>
       <c r="V2" t="n">
-        <v>1.279080606764182e-06</v>
+        <v>0.07321314513683319</v>
       </c>
       <c r="W2" t="n">
-        <v>1.858564610301983e-05</v>
+        <v>0.04436027631163597</v>
       </c>
       <c r="X2" t="n">
-        <v>2.603900065878406e-05</v>
+        <v>0.04681634902954102</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.674876330071129e-06</v>
+        <v>0.06209565699100494</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.256848645425634e-05</v>
+        <v>0.0029630521312356</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.133612724719569e-06</v>
+        <v>0.09172295778989792</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.737362410698552e-05</v>
+        <v>0.05743616074323654</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.543309710745234e-05</v>
+        <v>0.03958547860383987</v>
       </c>
       <c r="AD2" t="n">
-        <v>7.781000022077933e-06</v>
+        <v>0.0364689789712429</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.757039171934593e-05</v>
+        <v>0.03045603260397911</v>
       </c>
       <c r="AF2" t="n">
-        <v>4.580178938340396e-05</v>
+        <v>0.0349515862762928</v>
       </c>
       <c r="AG2" t="n">
-        <v>9.106909601541702e-06</v>
+        <v>0.01461428962647915</v>
       </c>
       <c r="AH2" t="n">
-        <v>7.681573151785415e-06</v>
+        <v>0.05966389551758766</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.675121767329983e-06</v>
+        <v>0.03656965494155884</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.717582381388638e-05</v>
+        <v>0.02840308099985123</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.029737152042799e-05</v>
+        <v>0.04436041414737701</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.953975465265103e-05</v>
+        <v>0.08251231908798218</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.923156782548176e-06</v>
+        <v>0.01994483545422554</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.537560092401691e-05</v>
+        <v>0.003282343968749046</v>
       </c>
       <c r="AO2" t="n">
-        <v>2.883356728489161e-06</v>
+        <v>0.1288043409585953</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.402941613079747e-06</v>
+        <v>0.01815102808177471</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.236207238747738e-06</v>
+        <v>0.02430460788309574</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.160887131845811e-05</v>
+        <v>0.001079537905752659</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.948366146592889e-06</v>
+        <v>0.03044183552265167</v>
       </c>
       <c r="AT2" t="n">
-        <v>2.209943340858445e-05</v>
+        <v>0.02681152895092964</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.242265873064753e-05</v>
+        <v>0.1616897135972977</v>
       </c>
       <c r="AV2" t="n">
-        <v>3.1501185731031e-06</v>
+        <v>0.02931027114391327</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.737869651056826e-05</v>
+        <v>0.02056523784995079</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.936443524959031e-05</v>
+        <v>0.02352722175419331</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.511842037871247e-05</v>
+        <v>0.03421055153012276</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.680542300164234e-05</v>
+        <v>0.03206013143062592</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.871075596682203e-07</v>
+        <v>0.01684446819126606</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.38746326128603e-06</v>
+        <v>0.03825270384550095</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.33755497194943e-06</v>
+        <v>0.01312699913978577</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.022004057129379e-05</v>
+        <v>0.214113861322403</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.857976131868782e-06</v>
+        <v>0.1001036018133163</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.644971729954705e-05</v>
+        <v>0.08775462955236435</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.356037607067265e-06</v>
+        <v>0.1747830957174301</v>
       </c>
       <c r="BH2" t="n">
-        <v>8.121409337036312e-06</v>
+        <v>0.03253037109971046</v>
       </c>
       <c r="BI2" t="n">
-        <v>4.653170890378533e-06</v>
+        <v>0.023385314270854</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2.100398432958173e-06</v>
+        <v>0.03455865010619164</v>
       </c>
       <c r="BK2" t="n">
-        <v>2.750420435404521e-06</v>
+        <v>0.03832585364580154</v>
       </c>
       <c r="BL2" t="n">
-        <v>3.376780659891665e-05</v>
+        <v>0.0105931218713522</v>
       </c>
       <c r="BM2" t="n">
-        <v>4.184376666671596e-05</v>
+        <v>0.0784844309091568</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.948642420757096e-07</v>
+        <v>0.008242193609476089</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.073755811376031e-05</v>
+        <v>0.08153112232685089</v>
       </c>
       <c r="BP2" t="n">
-        <v>1.171796611743048e-06</v>
+        <v>0.08794886618852615</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.494761704634584e-06</v>
+        <v>0.001771306968294084</v>
       </c>
       <c r="BR2" t="n">
-        <v>6.880673026898876e-06</v>
+        <v>0.06786976009607315</v>
       </c>
       <c r="BS2" t="n">
-        <v>2.727500259425142e-06</v>
+        <v>0.01034745387732983</v>
       </c>
       <c r="BT2" t="n">
-        <v>9.346810657007154e-06</v>
+        <v>0.006352560129016638</v>
       </c>
       <c r="BU2" t="n">
-        <v>2.768559716059826e-05</v>
+        <v>0.06498177349567413</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.207756187999621e-05</v>
+        <v>0.1403293460607529</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.356558072984626e-06</v>
+        <v>0.008838907815515995</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.995388265640941e-05</v>
+        <v>0.09730495512485504</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.457520738767926e-05</v>
+        <v>0.05478732287883759</v>
       </c>
       <c r="BZ2" t="n">
-        <v>8.958427315519657e-06</v>
+        <v>0.03611283749341965</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.06226416392019e-05</v>
+        <v>0.06859524548053741</v>
       </c>
       <c r="CB2" t="n">
-        <v>6.538737125083571e-06</v>
+        <v>0.007424906827509403</v>
       </c>
       <c r="CC2" t="n">
-        <v>1.727400012896396e-05</v>
+        <v>0.07063616812229156</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.699817585176788e-05</v>
+        <v>0.01230657286942005</v>
       </c>
       <c r="CE2" t="n">
-        <v>4.787078069057316e-06</v>
+        <v>0.05913149192929268</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.800688434945187e-06</v>
+        <v>0.03652168810367584</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.719058647926431e-05</v>
+        <v>0.07119239866733551</v>
       </c>
       <c r="CH2" t="n">
-        <v>9.403148396813776e-06</v>
+        <v>0.01893365755677223</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.127697851188714e-05</v>
+        <v>0.005301306489855051</v>
       </c>
       <c r="CJ2" t="n">
-        <v>6.073601070966106e-06</v>
+        <v>0.02026974223554134</v>
       </c>
       <c r="CK2" t="n">
-        <v>7.28566055840929e-06</v>
+        <v>0.01347488537430763</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.664664407348027e-06</v>
+        <v>0.002132966415956616</v>
       </c>
       <c r="CM2" t="n">
-        <v>4.637644906324567e-06</v>
+        <v>0.04312668740749359</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.527682227082551e-06</v>
+        <v>0.002640184015035629</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.347108081972692e-06</v>
+        <v>0.001016297377645969</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.186058191000484e-05</v>
+        <v>0.09409512579441071</v>
       </c>
       <c r="CQ2" t="n">
-        <v>9.138337190961465e-06</v>
+        <v>0.08156812936067581</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.985643393709324e-06</v>
+        <v>0.008729198947548866</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.706401548697613e-05</v>
+        <v>0.003297613933682442</v>
       </c>
       <c r="CT2" t="n">
-        <v>4.877160245086998e-05</v>
+        <v>0.01401761639863253</v>
       </c>
       <c r="CU2" t="n">
-        <v>2.548379234212916e-05</v>
+        <v>0.004374512936919928</v>
       </c>
       <c r="CV2" t="n">
-        <v>1.91278122656513e-05</v>
+        <v>0.02123911306262016</v>
       </c>
       <c r="CW2" t="n">
-        <v>7.908423867775127e-06</v>
+        <v>0.05775173380970955</v>
       </c>
       <c r="CX2" t="n">
-        <v>3.850097073154757e-06</v>
+        <v>0.03013498708605766</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.259600660181604e-05</v>
+        <v>0.06557790189981461</v>
       </c>
       <c r="CZ2" t="n">
-        <v>6.375808879965916e-06</v>
+        <v>0.003983707167208195</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.665625131863635e-05</v>
+        <v>0.001081853988580406</v>
       </c>
       <c r="DB2" t="n">
-        <v>3.35795630235225e-06</v>
+        <v>0.02000589296221733</v>
       </c>
       <c r="DC2" t="n">
-        <v>5.608307219517883e-06</v>
+        <v>0.01296354457736015</v>
       </c>
       <c r="DD2" t="n">
-        <v>3.497895932014217e-06</v>
+        <v>0.008361892774701118</v>
       </c>
       <c r="DE2" t="n">
-        <v>3.427338924666401e-06</v>
+        <v>0.0160469114780426</v>
       </c>
       <c r="DF2" t="n">
-        <v>6.005336399539374e-05</v>
+        <v>0.1743715405464172</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.322701013530605e-05</v>
+        <v>0.06781944632530212</v>
       </c>
       <c r="DH2" t="n">
-        <v>1.823858110583387e-05</v>
+        <v>0.02389787510037422</v>
       </c>
       <c r="DI2" t="n">
-        <v>2.70585387625033e-05</v>
+        <v>0.005397689528763294</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.775221921387129e-05</v>
+        <v>0.0349435955286026</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.974389958078973e-05</v>
+        <v>0.0271095335483551</v>
       </c>
       <c r="DL2" t="n">
-        <v>5.029707608628087e-06</v>
+        <v>0.003321503521874547</v>
       </c>
       <c r="DM2" t="n">
-        <v>2.448593841108959e-05</v>
+        <v>0.03712199628353119</v>
       </c>
       <c r="DN2" t="n">
-        <v>2.0136092643952e-05</v>
+        <v>0.02472627721726894</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.013246856018668e-05</v>
+        <v>0.0421893447637558</v>
       </c>
       <c r="DP2" t="n">
-        <v>2.953794682980515e-05</v>
+        <v>0.0462048351764679</v>
       </c>
       <c r="DQ2" t="n">
-        <v>3.281303361291066e-05</v>
+        <v>0.03922533243894577</v>
       </c>
       <c r="DR2" t="n">
-        <v>2.736860096774762e-06</v>
+        <v>0.0388387069106102</v>
       </c>
       <c r="DS2" t="n">
-        <v>8.697052180650644e-06</v>
+        <v>0.1182504221796989</v>
       </c>
       <c r="DT2" t="n">
-        <v>5.388488716562279e-06</v>
+        <v>0.07836209237575531</v>
       </c>
       <c r="DU2" t="n">
-        <v>3.870238288072869e-06</v>
+        <v>0.0889902263879776</v>
       </c>
       <c r="DV2" t="n">
-        <v>9.953812877938617e-06</v>
+        <v>0.05974745005369186</v>
       </c>
       <c r="DW2" t="n">
-        <v>2.69046904577408e-05</v>
+        <v>0.03466911241412163</v>
       </c>
       <c r="DX2" t="n">
-        <v>1.109183358494192e-05</v>
+        <v>0.009230862371623516</v>
       </c>
       <c r="DY2" t="n">
-        <v>1.11941608338384e-05</v>
+        <v>0.06242664903402328</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.388270356983412e-05</v>
+        <v>0.08629730343818665</v>
       </c>
       <c r="EA2" t="n">
-        <v>1.221739148604684e-05</v>
+        <v>0.20210200548172</v>
       </c>
       <c r="EB2" t="n">
-        <v>2.354566095164046e-05</v>
+        <v>0.1663567423820496</v>
       </c>
       <c r="EC2" t="n">
-        <v>1.571878419781569e-05</v>
+        <v>0.002886313712224364</v>
       </c>
       <c r="ED2" t="n">
-        <v>2.773849155346397e-05</v>
+        <v>0.08996482938528061</v>
       </c>
       <c r="EE2" t="n">
-        <v>7.229837592603872e-06</v>
+        <v>0.04442604258656502</v>
       </c>
       <c r="EF2" t="n">
-        <v>6.041768756404053e-07</v>
+        <v>0.04768469929695129</v>
       </c>
       <c r="EG2" t="n">
-        <v>2.761450332400273e-06</v>
+        <v>0.05011224746704102</v>
       </c>
       <c r="EH2" t="n">
-        <v>1.65719688993704e-06</v>
+        <v>0.02269918844103813</v>
       </c>
       <c r="EI2" t="n">
-        <v>4.833114508073777e-05</v>
+        <v>0.1468453705310822</v>
       </c>
       <c r="EJ2" t="n">
-        <v>8.587338015786372e-06</v>
+        <v>0.006264407187700272</v>
       </c>
       <c r="EK2" t="n">
-        <v>8.631486707599834e-06</v>
+        <v>0.04184596985578537</v>
       </c>
       <c r="EL2" t="n">
-        <v>1.400332166667795e-06</v>
+        <v>0.006650066003203392</v>
       </c>
       <c r="EM2" t="n">
-        <v>1.411632365488913e-05</v>
+        <v>0.007833825424313545</v>
       </c>
       <c r="EN2" t="n">
-        <v>5.205230991123244e-06</v>
+        <v>0.02047738619148731</v>
       </c>
       <c r="EO2" t="n">
-        <v>2.802246854116675e-05</v>
+        <v>0.008168449625372887</v>
       </c>
       <c r="EP2" t="n">
-        <v>1.02428998616233e-06</v>
+        <v>0.06702541559934616</v>
       </c>
       <c r="EQ2" t="n">
-        <v>2.197150752181187e-05</v>
+        <v>0.003488990711048245</v>
       </c>
       <c r="ER2" t="n">
-        <v>1.829323809943162e-05</v>
+        <v>0.0162161011248827</v>
       </c>
       <c r="ES2" t="n">
-        <v>2.657544882822549e-06</v>
+        <v>0.01783411204814911</v>
       </c>
       <c r="ET2" t="n">
-        <v>3.480237501207739e-05</v>
+        <v>0.0006937198340892792</v>
       </c>
       <c r="EU2" t="n">
-        <v>4.805858225154225e-06</v>
+        <v>0.002863621339201927</v>
       </c>
       <c r="EV2" t="n">
-        <v>1.317619080509758e-05</v>
+        <v>0.0007832101546227932</v>
       </c>
       <c r="EW2" t="n">
-        <v>1.063894615072059e-05</v>
+        <v>0.03049734234809875</v>
       </c>
       <c r="EX2" t="n">
-        <v>2.276476880069822e-05</v>
+        <v>0.01261212211102247</v>
       </c>
       <c r="EY2" t="n">
-        <v>6.736626346537378e-06</v>
+        <v>0.0769796222448349</v>
       </c>
       <c r="EZ2" t="n">
-        <v>4.843964234169107e-06</v>
+        <v>0.03019843995571136</v>
       </c>
       <c r="FA2" t="n">
-        <v>2.599408799142111e-05</v>
+        <v>0.0486178807914257</v>
       </c>
       <c r="FB2" t="n">
-        <v>1.142358087236062e-05</v>
+        <v>0.00271712988615036</v>
       </c>
       <c r="FC2" t="n">
-        <v>1.164094555861084e-05</v>
+        <v>0.009232450276613235</v>
       </c>
       <c r="FD2" t="n">
-        <v>9.842760846368037e-07</v>
+        <v>0.01163359172642231</v>
       </c>
       <c r="FE2" t="n">
-        <v>2.765020781225758e-06</v>
+        <v>0.006411232054233551</v>
       </c>
       <c r="FF2" t="n">
-        <v>1.002447243081406e-05</v>
+        <v>0.003202660940587521</v>
       </c>
       <c r="FG2" t="n">
-        <v>1.062316823663423e-05</v>
+        <v>0.04292948544025421</v>
       </c>
       <c r="FH2" t="n">
-        <v>2.98685954476241e-05</v>
+        <v>0.1067823767662048</v>
       </c>
       <c r="FI2" t="n">
-        <v>3.161727136102854e-06</v>
+        <v>0.06914519518613815</v>
       </c>
       <c r="FJ2" t="n">
-        <v>1.346133831248153e-05</v>
+        <v>0.05055095255374908</v>
       </c>
       <c r="FK2" t="n">
-        <v>1.58780694619054e-05</v>
+        <v>0.07256579399108887</v>
       </c>
       <c r="FL2" t="n">
-        <v>1.44227669807151e-06</v>
+        <v>0.04467529430985451</v>
       </c>
       <c r="FM2" t="n">
-        <v>1.588656050444115e-05</v>
+        <v>0.03293301537632942</v>
       </c>
       <c r="FN2" t="n">
-        <v>1.086864085664274e-05</v>
+        <v>0.1618913263082504</v>
       </c>
       <c r="FO2" t="n">
-        <v>4.542354872683063e-06</v>
+        <v>0.07268434762954712</v>
       </c>
       <c r="FP2" t="n">
-        <v>3.784450382227078e-05</v>
+        <v>0.1126320585608482</v>
       </c>
       <c r="FQ2" t="n">
-        <v>3.013462264789268e-05</v>
+        <v>0.03709900751709938</v>
       </c>
       <c r="FR2" t="n">
-        <v>9.53305971052032e-07</v>
+        <v>0.1005077585577965</v>
       </c>
       <c r="FS2" t="n">
-        <v>2.586841674201423e-06</v>
+        <v>0.1432432532310486</v>
       </c>
       <c r="FT2" t="n">
-        <v>9.15068721951684e-06</v>
+        <v>0.07639101147651672</v>
       </c>
       <c r="FU2" t="n">
-        <v>1.066069580701878e-05</v>
+        <v>0.06678871065378189</v>
       </c>
       <c r="FV2" t="n">
-        <v>6.799553375458345e-05</v>
+        <v>0.006390117108821869</v>
       </c>
       <c r="FW2" t="n">
-        <v>3.361298877280205e-05</v>
+        <v>0.0552191324532032</v>
       </c>
       <c r="FX2" t="n">
-        <v>8.861562491802033e-06</v>
+        <v>0.08357382565736771</v>
       </c>
       <c r="FY2" t="n">
-        <v>4.946364060742781e-05</v>
+        <v>0.009400296024978161</v>
       </c>
       <c r="FZ2" t="n">
-        <v>5.208874426898547e-06</v>
+        <v>0.02262879908084869</v>
       </c>
       <c r="GA2" t="n">
-        <v>4.152228211751208e-05</v>
+        <v>0.01858669891953468</v>
       </c>
       <c r="GB2" t="n">
-        <v>2.928381945821457e-06</v>
+        <v>0.01360271498560905</v>
       </c>
       <c r="GC2" t="n">
-        <v>3.897691931342706e-05</v>
+        <v>0.06049428880214691</v>
       </c>
       <c r="GD2" t="n">
-        <v>2.214713276771363e-05</v>
+        <v>0.04452673345804214</v>
       </c>
       <c r="GE2" t="n">
-        <v>3.514525087666698e-05</v>
+        <v>0.06535732001066208</v>
       </c>
       <c r="GF2" t="n">
-        <v>2.119813325407449e-05</v>
+        <v>0.005622974131256342</v>
       </c>
       <c r="GG2" t="n">
-        <v>2.092780232487712e-05</v>
+        <v>0.03661787509918213</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0</v>
+        <v>0.02550175786018372</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.002389592118561268</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.007040335796773434</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>0.01909572258591652</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.0009309325832873583</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.008146117441356182</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.02089332230389118</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>0.01154910400509834</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.0005190380616113544</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.0338619090616703</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>0.002638667589053512</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.005000501405447721</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.009697940200567245</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.02269351482391357</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.007135961204767227</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.0343475416302681</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.003797580022364855</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>0.02016429603099823</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.004553489852696657</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.002234330167993903</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.001178793725557625</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.00367905804887414</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.002642213366925716</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.006103838328272104</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.004124369937926531</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>0.00412539578974247</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>7.576687494292855e-05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>0.001190001145005226</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.006550981663167477</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>0.002353080082684755</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.001119598047807813</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.006567660719156265</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>0.01085794623941183</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.002149946521967649</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>0.006848959252238274</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.0004138652002438903</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>0.002287780167534947</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>0.01064297743141651</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>0.006937277503311634</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>0.001202690764330328</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>0.008796402253210545</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.003547015599906445</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>0.002426565857604146</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.002940776525065303</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>0.002897338941693306</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>0.02047904394567013</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.003424305003136396</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>0.004827996715903282</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>0.005973090883344412</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>8.247164078056812e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>0.001292853732593358</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.01230463199317455</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>0.01364003866910934</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>0.003509202040731907</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>0.007520738523453474</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>0.002750998362898827</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>0.00138122052885592</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>0.01332071796059608</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>0.006303769070655107</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>0.007570482790470123</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>0.002023846842348576</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.0099589629098773</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.005145501811057329</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>0.007157091982662678</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.002819041488692164</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>0.002257617423310876</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.001475247321650386</v>
       </c>
       <c r="BP3" t="n">
-        <v>0</v>
+        <v>0.007112464401870966</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0</v>
+        <v>0.00444047711789608</v>
       </c>
       <c r="BR3" t="n">
-        <v>0</v>
+        <v>0.004411662928760052</v>
       </c>
       <c r="BS3" t="n">
-        <v>0</v>
+        <v>0.008176838979125023</v>
       </c>
       <c r="BT3" t="n">
-        <v>0</v>
+        <v>0.007682160474359989</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>0.008032301440834999</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>0.005794761702418327</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>0.005023076198995113</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>0.007149116601794958</v>
       </c>
       <c r="BY3" t="n">
-        <v>0</v>
+        <v>0.002717965980991721</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>0.0005076194065622985</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>0.009495822712779045</v>
       </c>
       <c r="CB3" t="n">
-        <v>0</v>
+        <v>0.001579698640853167</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>0.004548351280391216</v>
       </c>
       <c r="CD3" t="n">
-        <v>0</v>
+        <v>0.008353644050657749</v>
       </c>
       <c r="CE3" t="n">
-        <v>0</v>
+        <v>0.005265662912279367</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>0.001738807884976268</v>
       </c>
       <c r="CG3" t="n">
-        <v>0</v>
+        <v>0.003452094737440348</v>
       </c>
       <c r="CH3" t="n">
-        <v>0</v>
+        <v>0.002297948114573956</v>
       </c>
       <c r="CI3" t="n">
-        <v>0</v>
+        <v>0.001248412649147213</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>0.004328086040914059</v>
       </c>
       <c r="CK3" t="n">
-        <v>0</v>
+        <v>0.001572844805195928</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>0.0007284021703526378</v>
       </c>
       <c r="CM3" t="n">
-        <v>0</v>
+        <v>0.004495946690440178</v>
       </c>
       <c r="CN3" t="n">
-        <v>0</v>
+        <v>0.02254689112305641</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>0.005812481511384249</v>
       </c>
       <c r="CP3" t="n">
-        <v>0</v>
+        <v>0.01240910403430462</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0</v>
+        <v>0.004690656438469887</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>0.01861884258687496</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>0.0154882837086916</v>
       </c>
       <c r="CT3" t="n">
-        <v>0</v>
+        <v>0.007075660862028599</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>0.008360554464161396</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>0.00813942588865757</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>0.004172837361693382</v>
       </c>
       <c r="CX3" t="n">
-        <v>0</v>
+        <v>0.003273995127528906</v>
       </c>
       <c r="CY3" t="n">
-        <v>0</v>
+        <v>0.002141032833606005</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0</v>
+        <v>0.004381102975457907</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>6.478674185927957e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>0.005307170562446117</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.002695761155337095</v>
       </c>
       <c r="DD3" t="n">
-        <v>0</v>
+        <v>0.0006365787703543901</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.01073877513408661</v>
       </c>
       <c r="DF3" t="n">
-        <v>0</v>
+        <v>0.008673973381519318</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>0.004962493199855089</v>
       </c>
       <c r="DH3" t="n">
-        <v>0</v>
+        <v>0.001602756325155497</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.01534246001392603</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0</v>
+        <v>0.008125824853777885</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>0.003986746538430452</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>0.004697435535490513</v>
       </c>
       <c r="DM3" t="n">
-        <v>0</v>
+        <v>0.004076739307492971</v>
       </c>
       <c r="DN3" t="n">
-        <v>0</v>
+        <v>0.001100956462323666</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>0.003162445733323693</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>0.001371121965348721</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.002031717216596007</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.002380705438554287</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>0.008269062265753746</v>
       </c>
       <c r="DT3" t="n">
-        <v>0</v>
+        <v>0.002495115855708718</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>0.003606873098760843</v>
       </c>
       <c r="DV3" t="n">
-        <v>0</v>
+        <v>0.001259952317923307</v>
       </c>
       <c r="DW3" t="n">
-        <v>0</v>
+        <v>0.002288915449753404</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>0.006004849914461374</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>0.0002650762908160686</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>0.0005625183694064617</v>
       </c>
       <c r="EA3" t="n">
-        <v>0</v>
+        <v>0.008747156709432602</v>
       </c>
       <c r="EB3" t="n">
-        <v>0</v>
+        <v>0.01306295953691006</v>
       </c>
       <c r="EC3" t="n">
-        <v>0</v>
+        <v>0.01902497000992298</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>0.00912361778318882</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>0.01294900476932526</v>
       </c>
       <c r="EF3" t="n">
-        <v>0</v>
+        <v>0.008017526939511299</v>
       </c>
       <c r="EG3" t="n">
-        <v>0</v>
+        <v>0.002580317901447415</v>
       </c>
       <c r="EH3" t="n">
-        <v>0</v>
+        <v>0.005047236103564501</v>
       </c>
       <c r="EI3" t="n">
-        <v>0</v>
+        <v>0.01516895741224289</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0</v>
+        <v>0.000854628044180572</v>
       </c>
       <c r="EK3" t="n">
-        <v>0</v>
+        <v>0.003481797408312559</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>0.004110145382583141</v>
       </c>
       <c r="EM3" t="n">
-        <v>0</v>
+        <v>0.004681591410189867</v>
       </c>
       <c r="EN3" t="n">
-        <v>0</v>
+        <v>0.004111144691705704</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>0.01018376834690571</v>
       </c>
       <c r="EP3" t="n">
-        <v>0</v>
+        <v>0.001645989716053009</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>0.005538632161915302</v>
       </c>
       <c r="ER3" t="n">
-        <v>0</v>
+        <v>0.003040851559489965</v>
       </c>
       <c r="ES3" t="n">
-        <v>0</v>
+        <v>0.01428721006959677</v>
       </c>
       <c r="ET3" t="n">
-        <v>0</v>
+        <v>0.007444897200912237</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>0.003321763593703508</v>
       </c>
       <c r="EV3" t="n">
-        <v>0</v>
+        <v>0.007187105715274811</v>
       </c>
       <c r="EW3" t="n">
-        <v>0</v>
+        <v>0.008758913725614548</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>0.01039211172610521</v>
       </c>
       <c r="EY3" t="n">
-        <v>0</v>
+        <v>0.007406544405966997</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>0.003423539455980062</v>
       </c>
       <c r="FA3" t="n">
-        <v>0</v>
+        <v>0.003815571079030633</v>
       </c>
       <c r="FB3" t="n">
-        <v>0</v>
+        <v>0.00341939739882946</v>
       </c>
       <c r="FC3" t="n">
-        <v>0</v>
+        <v>0.003452865872532129</v>
       </c>
       <c r="FD3" t="n">
-        <v>0</v>
+        <v>0.007090323138982058</v>
       </c>
       <c r="FE3" t="n">
-        <v>0</v>
+        <v>0.00294940173625946</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>0.002517449902370572</v>
       </c>
       <c r="FG3" t="n">
-        <v>0</v>
+        <v>0.006505159195512533</v>
       </c>
       <c r="FH3" t="n">
-        <v>0</v>
+        <v>0.007583432830870152</v>
       </c>
       <c r="FI3" t="n">
-        <v>0</v>
+        <v>0.004146549850702286</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0</v>
+        <v>0.001071200706064701</v>
       </c>
       <c r="FK3" t="n">
-        <v>0</v>
+        <v>0.007749041076749563</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>0.004392894450575113</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>0.003146177856251597</v>
       </c>
       <c r="FN3" t="n">
-        <v>0</v>
+        <v>0.003596444148570299</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>0.001769819296896458</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>0.01239216607064009</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0</v>
+        <v>0.0251288078725338</v>
       </c>
       <c r="FR3" t="n">
-        <v>0</v>
+        <v>0.01883167773485184</v>
       </c>
       <c r="FS3" t="n">
-        <v>0</v>
+        <v>0.00669699814170599</v>
       </c>
       <c r="FT3" t="n">
-        <v>0</v>
+        <v>0.0155459176748991</v>
       </c>
       <c r="FU3" t="n">
-        <v>0</v>
+        <v>0.006792945321649313</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>0.00791064091026783</v>
       </c>
       <c r="FW3" t="n">
-        <v>0</v>
+        <v>0.001343672862276435</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>0.005160588305443525</v>
       </c>
       <c r="FY3" t="n">
-        <v>0</v>
+        <v>0.005922550335526466</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0</v>
+        <v>0.004572471603751183</v>
       </c>
       <c r="GA3" t="n">
-        <v>0</v>
+        <v>0.00829547643661499</v>
       </c>
       <c r="GB3" t="n">
-        <v>0</v>
+        <v>0.008518699556589127</v>
       </c>
       <c r="GC3" t="n">
-        <v>0</v>
+        <v>0.005234332289546728</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>0.003360387403517962</v>
       </c>
       <c r="GE3" t="n">
-        <v>0</v>
+        <v>0.01415300741791725</v>
       </c>
       <c r="GF3" t="n">
-        <v>0</v>
+        <v>0.005397944711148739</v>
       </c>
       <c r="GG3" t="n">
+        <v>0.003708473406732082</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>0.2424487769603729</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9077291488647461</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0491335466504097</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2100973427295685</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1787823587656021</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8431630730628967</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1170796006917953</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1460619270801544</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03485453873872757</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.08406155556440353</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9832716584205627</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.05068638920783997</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1825129687786102</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2223469763994217</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6789962649345398</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1675674915313721</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1473620980978012</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.01195026561617851</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1048932299017906</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.2631583511829376</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.3283220827579498</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.1992663443088531</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1633646041154861</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.1549549996852875</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.4504987299442291</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.2451724708080292</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.115082636475563</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.2637738585472107</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.2246187031269073</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.1040612906217575</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.5381928086280823</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.1262987703084946</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.2316061109304428</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.2305673211812973</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2874117493629456</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.2562020421028137</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.01892909035086632</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.07087048143148422</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.01470988243818283</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.06813880056142807</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.1023213490843773</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.2257826775312424</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.2985537350177765</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.1471890956163406</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.04241618514060974</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.04527150839567184</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.4847390949726105</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.1509058922529221</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1494673639535904</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.4892479181289673</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.5497007369995117</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.2129077464342117</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0.09595592319965363</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>0.1501550823450089</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.1445855051279068</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.5714274644851685</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.146210104227066</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.4102959334850311</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.4051920473575592</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.2669641971588135</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>0.09090051054954529</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.2495003789663315</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.1558930575847626</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.09799207746982574</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.02549838274717331</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.06095262989401817</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.02099315822124481</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.1433673202991486</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.1715134680271149</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.03899513930082321</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.1099588572978973</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.07000943273305893</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.0513065829873085</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.1881633996963501</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.2795296907424927</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.1294260621070862</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.1878578662872314</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.4170668125152588</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.4907200634479523</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.07165753096342087</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>0.004842078313231468</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>0.06010322645306587</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.2852502167224884</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.04787448793649673</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.1019335314631462</v>
+      </c>
+      <c r="CH4" t="n">
+        <v>0.03476222977042198</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.1787859499454498</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.02526780404150486</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.0005226344801485538</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.02530370280146599</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.3253856897354126</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.5781958699226379</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>0.4081988334655762</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>0.2302390784025192</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.007619630545377731</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.2512239813804626</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.006498092319816351</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.1446407437324524</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.2020163089036942</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.04530643671751022</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>0.2569379210472107</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>0.002778495661914349</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.05715654045343399</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.01815837994217873</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.1474431157112122</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.04358505457639694</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.04243398085236549</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.0009321849793195724</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>0.4161494970321655</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.09739300608634949</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.2576443552970886</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.1340631544589996</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.132337898015976</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0.5102260112762451</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>0.1637679040431976</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.09668668359518051</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>0.2124413698911667</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.03123269602656364</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>0.186650425195694</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>0.05928386002779007</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.2936348021030426</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.07549671828746796</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.04419735446572304</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.05995793268084526</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0.0795615017414093</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>0.04642031341791153</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.1364992558956146</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>0.2485716342926025</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>0.05672217160463333</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>0.05505482852458954</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>0.2450242638587952</v>
+      </c>
+      <c r="EB4" t="n">
+        <v>0.2942231893539429</v>
+      </c>
+      <c r="EC4" t="n">
+        <v>0.05196452140808105</v>
+      </c>
+      <c r="ED4" t="n">
+        <v>0.2868527770042419</v>
+      </c>
+      <c r="EE4" t="n">
+        <v>0.289000391960144</v>
+      </c>
+      <c r="EF4" t="n">
+        <v>0.0747009664773941</v>
+      </c>
+      <c r="EG4" t="n">
+        <v>0.1046542376279831</v>
+      </c>
+      <c r="EH4" t="n">
+        <v>0.1205196678638458</v>
+      </c>
+      <c r="EI4" t="n">
+        <v>0.2133752107620239</v>
+      </c>
+      <c r="EJ4" t="n">
+        <v>0.01391056552529335</v>
+      </c>
+      <c r="EK4" t="n">
+        <v>0.2260077744722366</v>
+      </c>
+      <c r="EL4" t="n">
+        <v>0.1051738411188126</v>
+      </c>
+      <c r="EM4" t="n">
+        <v>0.106570802628994</v>
+      </c>
+      <c r="EN4" t="n">
+        <v>0.03543355315923691</v>
+      </c>
+      <c r="EO4" t="n">
+        <v>0.07221202552318573</v>
+      </c>
+      <c r="EP4" t="n">
+        <v>0.1687722653150558</v>
+      </c>
+      <c r="EQ4" t="n">
+        <v>0.224968820810318</v>
+      </c>
+      <c r="ER4" t="n">
+        <v>0.1659468114376068</v>
+      </c>
+      <c r="ES4" t="n">
+        <v>0.2802038788795471</v>
+      </c>
+      <c r="ET4" t="n">
+        <v>0.2870596349239349</v>
+      </c>
+      <c r="EU4" t="n">
+        <v>0.03812901675701141</v>
+      </c>
+      <c r="EV4" t="n">
+        <v>0.09718170762062073</v>
+      </c>
+      <c r="EW4" t="n">
+        <v>0.03224460780620575</v>
+      </c>
+      <c r="EX4" t="n">
+        <v>0.05319366604089737</v>
+      </c>
+      <c r="EY4" t="n">
+        <v>0.2456785291433334</v>
+      </c>
+      <c r="EZ4" t="n">
+        <v>0.01077468134462833</v>
+      </c>
+      <c r="FA4" t="n">
+        <v>0.04174049943685532</v>
+      </c>
+      <c r="FB4" t="n">
+        <v>0.08923165500164032</v>
+      </c>
+      <c r="FC4" t="n">
+        <v>0.1667132824659348</v>
+      </c>
+      <c r="FD4" t="n">
+        <v>0.01150083169341087</v>
+      </c>
+      <c r="FE4" t="n">
+        <v>0.004745054990053177</v>
+      </c>
+      <c r="FF4" t="n">
+        <v>0.03013306297361851</v>
+      </c>
+      <c r="FG4" t="n">
+        <v>0.2258945256471634</v>
+      </c>
+      <c r="FH4" t="n">
+        <v>0.04525819420814514</v>
+      </c>
+      <c r="FI4" t="n">
+        <v>0.1137455180287361</v>
+      </c>
+      <c r="FJ4" t="n">
+        <v>0.01147140190005302</v>
+      </c>
+      <c r="FK4" t="n">
+        <v>0.1964482069015503</v>
+      </c>
+      <c r="FL4" t="n">
+        <v>0.2600796222686768</v>
+      </c>
+      <c r="FM4" t="n">
+        <v>0.1514255851507187</v>
+      </c>
+      <c r="FN4" t="n">
+        <v>0.1866495013237</v>
+      </c>
+      <c r="FO4" t="n">
+        <v>0.3435436189174652</v>
+      </c>
+      <c r="FP4" t="n">
+        <v>0.4987988471984863</v>
+      </c>
+      <c r="FQ4" t="n">
+        <v>0.2438699901103973</v>
+      </c>
+      <c r="FR4" t="n">
+        <v>0.03517989814281464</v>
+      </c>
+      <c r="FS4" t="n">
+        <v>0.0315706878900528</v>
+      </c>
+      <c r="FT4" t="n">
+        <v>0.03564508259296417</v>
+      </c>
+      <c r="FU4" t="n">
+        <v>0.00654793344438076</v>
+      </c>
+      <c r="FV4" t="n">
+        <v>0.1064743921160698</v>
+      </c>
+      <c r="FW4" t="n">
+        <v>0.004389133304357529</v>
+      </c>
+      <c r="FX4" t="n">
+        <v>0.07038553059101105</v>
+      </c>
+      <c r="FY4" t="n">
+        <v>0.258063405752182</v>
+      </c>
+      <c r="FZ4" t="n">
+        <v>0.0737711489200592</v>
+      </c>
+      <c r="GA4" t="n">
+        <v>0.05954514443874359</v>
+      </c>
+      <c r="GB4" t="n">
+        <v>0.03296789899468422</v>
+      </c>
+      <c r="GC4" t="n">
+        <v>0.3164591789245605</v>
+      </c>
+      <c r="GD4" t="n">
+        <v>0.2268644571304321</v>
+      </c>
+      <c r="GE4" t="n">
+        <v>0.1542892307043076</v>
+      </c>
+      <c r="GF4" t="n">
+        <v>0.198424756526947</v>
+      </c>
+      <c r="GG4" t="n">
+        <v>0.3167748749256134</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>0.06454914808273315</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2681466042995453</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.08004899322986603</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.002955000847578049</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.02102874591946602</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2959299683570862</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.04677188396453857</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1019489169120789</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.05240596458315849</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.02017917670309544</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.3351986408233643</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1028699651360512</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.07076522707939148</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1283254623413086</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.3127173185348511</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.02581500262022018</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.01358398608863354</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.05346484109759331</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.001482908031903207</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.04478275403380394</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.0493701845407486</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.106244370341301</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.09539591521024704</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.05068613961338997</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.002197034657001495</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.03727900981903076</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.03811113908886909</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.01033494528383017</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.04932289943099022</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.04088835790753365</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.09153848141431808</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.1245479509234428</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.04762275516986847</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.008825484663248062</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.1831098347902298</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.008982548490166664</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.004610017873346806</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.07429303228855133</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.04127655178308487</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.06335265934467316</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.03367960080504417</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.02413791045546532</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.02349730581045151</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.06826578825712204</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.06682921946048737</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.0292167030274868</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.3531465530395508</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.06593610346317291</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.02749128639698029</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.09538432955741882</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.1760297566652298</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.04307479038834572</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.009341243654489517</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.03932305797934532</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.009405247867107391</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.05817313119769096</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.05818355828523636</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.007013177499175072</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.01294539961963892</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.005487142596393824</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.02607679180800915</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.05214506760239601</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.01360285468399525</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.02666763961315155</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.05392523854970932</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.01085487380623817</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.04386873915791512</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.02993350848555565</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.04203590005636215</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.1344222724437714</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.0006818827241659164</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.04936572909355164</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0.01398518308997154</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.2092384397983551</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.04327978938817978</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.1143993139266968</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.05182977765798569</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.1216135397553444</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.0225642379373312</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.0006688470020890236</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.04629687592387199</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.009660651907324791</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.09400548040866852</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.01117059588432312</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.02957550063729286</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.001427446492016315</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.06761381030082703</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.03582426160573959</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.01915884763002396</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.02133710123598576</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.06384798884391785</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.1349340230226517</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>0.07365430891513824</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>0.0902663916349411</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.050584826618433</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.007101222407072783</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.05874334275722504</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.005422629415988922</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.005019050557166338</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.008082322776317596</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>0.0812610387802124</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>0.01599015295505524</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.01796584390103817</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.006656351499259472</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.07552053034305573</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.02263541892170906</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.01550689339637756</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.01795754581689835</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>0.04404797405004501</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.02425728179514408</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.05378422141075134</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.01185103878378868</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0.05183599144220352</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.07780256122350693</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>0.02146367356181145</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.07269938290119171</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>0.008590374141931534</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.01929932460188866</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>0.04373318701982498</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>0.009081737138330936</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.03908924013376236</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.02161114104092121</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0.02791462652385235</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0.01158066466450691</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0.04681088030338287</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>0.03448126837611198</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0.03523839265108109</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>0.01942707970738411</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>0.04594465345144272</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>0.04561962932348251</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>1.847883686423302e-05</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>0.08470889180898666</v>
+      </c>
+      <c r="EC6" t="n">
+        <v>0.002147779567167163</v>
+      </c>
+      <c r="ED6" t="n">
+        <v>0.002108761109411716</v>
+      </c>
+      <c r="EE6" t="n">
+        <v>0.06280114501714706</v>
+      </c>
+      <c r="EF6" t="n">
+        <v>0.001657695975154638</v>
+      </c>
+      <c r="EG6" t="n">
+        <v>0.006579683162271976</v>
+      </c>
+      <c r="EH6" t="n">
+        <v>0.01887603476643562</v>
+      </c>
+      <c r="EI6" t="n">
+        <v>0.08729533851146698</v>
+      </c>
+      <c r="EJ6" t="n">
+        <v>0.03490611910820007</v>
+      </c>
+      <c r="EK6" t="n">
+        <v>0.03615769743919373</v>
+      </c>
+      <c r="EL6" t="n">
+        <v>0.005479037296026945</v>
+      </c>
+      <c r="EM6" t="n">
+        <v>0.004365129396319389</v>
+      </c>
+      <c r="EN6" t="n">
+        <v>0.02093986049294472</v>
+      </c>
+      <c r="EO6" t="n">
+        <v>0.001864384859800339</v>
+      </c>
+      <c r="EP6" t="n">
+        <v>0.05012649297714233</v>
+      </c>
+      <c r="EQ6" t="n">
+        <v>0.0240339282900095</v>
+      </c>
+      <c r="ER6" t="n">
+        <v>0.00842459499835968</v>
+      </c>
+      <c r="ES6" t="n">
+        <v>0.04315432906150818</v>
+      </c>
+      <c r="ET6" t="n">
+        <v>0.02710783667862415</v>
+      </c>
+      <c r="EU6" t="n">
+        <v>0.01949974521994591</v>
+      </c>
+      <c r="EV6" t="n">
+        <v>0.01802581548690796</v>
+      </c>
+      <c r="EW6" t="n">
+        <v>0.002016489859670401</v>
+      </c>
+      <c r="EX6" t="n">
+        <v>0.004036008380353451</v>
+      </c>
+      <c r="EY6" t="n">
+        <v>0.09832505881786346</v>
+      </c>
+      <c r="EZ6" t="n">
+        <v>0.01243448350578547</v>
+      </c>
+      <c r="FA6" t="n">
+        <v>0.01811332255601883</v>
+      </c>
+      <c r="FB6" t="n">
+        <v>0.00959312915802002</v>
+      </c>
+      <c r="FC6" t="n">
+        <v>0.07047367095947266</v>
+      </c>
+      <c r="FD6" t="n">
+        <v>0.03985875844955444</v>
+      </c>
+      <c r="FE6" t="n">
+        <v>0.0185587964951992</v>
+      </c>
+      <c r="FF6" t="n">
+        <v>0.0009948041988536716</v>
+      </c>
+      <c r="FG6" t="n">
+        <v>0.0004548639990389347</v>
+      </c>
+      <c r="FH6" t="n">
+        <v>0.08600321412086487</v>
+      </c>
+      <c r="FI6" t="n">
+        <v>0.04526842385530472</v>
+      </c>
+      <c r="FJ6" t="n">
+        <v>0.01558824628591537</v>
+      </c>
+      <c r="FK6" t="n">
+        <v>0.01720945164561272</v>
+      </c>
+      <c r="FL6" t="n">
+        <v>0.0925295352935791</v>
+      </c>
+      <c r="FM6" t="n">
+        <v>0.04737678170204163</v>
+      </c>
+      <c r="FN6" t="n">
+        <v>0.1235438287258148</v>
+      </c>
+      <c r="FO6" t="n">
+        <v>0.08220665901899338</v>
+      </c>
+      <c r="FP6" t="n">
+        <v>0.03730998560786247</v>
+      </c>
+      <c r="FQ6" t="n">
+        <v>0.1021320074796677</v>
+      </c>
+      <c r="FR6" t="n">
+        <v>0.05835826694965363</v>
+      </c>
+      <c r="FS6" t="n">
+        <v>0.07638007402420044</v>
+      </c>
+      <c r="FT6" t="n">
+        <v>0.04398330673575401</v>
+      </c>
+      <c r="FU6" t="n">
+        <v>0.08836664259433746</v>
+      </c>
+      <c r="FV6" t="n">
+        <v>0.02150371484458447</v>
+      </c>
+      <c r="FW6" t="n">
+        <v>0.1169412061572075</v>
+      </c>
+      <c r="FX6" t="n">
+        <v>0.05548575520515442</v>
+      </c>
+      <c r="FY6" t="n">
+        <v>0.03377846628427505</v>
+      </c>
+      <c r="FZ6" t="n">
+        <v>0.00593084841966629</v>
+      </c>
+      <c r="GA6" t="n">
+        <v>0.05645953863859177</v>
+      </c>
+      <c r="GB6" t="n">
+        <v>0.01774147152900696</v>
+      </c>
+      <c r="GC6" t="n">
+        <v>0.105535551905632</v>
+      </c>
+      <c r="GD6" t="n">
+        <v>0.08189113438129425</v>
+      </c>
+      <c r="GE6" t="n">
+        <v>0.02364852279424667</v>
+      </c>
+      <c r="GF6" t="n">
+        <v>0.01992233842611313</v>
+      </c>
+      <c r="GG6" t="n">
+        <v>0.05298028141260147</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>0.3662444353103638</v>
+      </c>
+      <c r="B7" t="n">
+        <v>0.4840022325515747</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.04866483807563782</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.03551417589187622</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.02188234217464924</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3993305563926697</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.1057099848985672</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.1762000471353531</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1471795737743378</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.348671555519104</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.6136265993118286</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.07723537087440491</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.07056774199008942</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.2038532495498657</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.3814215362071991</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1205804497003555</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.02617419324815273</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.2587722539901733</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.02476547658443451</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.07505714148283005</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.0917772576212883</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1628804057836533</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.1136727854609489</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.08857278525829315</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.01962941139936447</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.1653937697410583</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.09107637405395508</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1189075708389282</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.1159706637263298</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.05489329993724823</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1770822703838348</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.2744313180446625</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.07385840266942978</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.01740498468279839</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.1751513779163361</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.06232656911015511</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.1184359788894653</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1527711451053619</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.1113006249070168</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.130822166800499</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.09358379244804382</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.02375587075948715</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.0812164843082428</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.1339459121227264</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.1326600313186646</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.2432147711515427</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.4355466067790985</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.07989031821489334</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.04436943680047989</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.1695198714733124</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.1480567455291748</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.02559267729520798</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0.006609579548239708</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.1079800426959991</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.0526583269238472</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.04770220816135406</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.07798019051551819</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.05906488746404648</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.003929156810045242</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.1530927568674088</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0.009077247232198715</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.05180447176098824</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.08489315956830978</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.01730110868811607</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.00375400111079216</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.003697566455230117</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.08796881139278412</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.001652011647820473</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0.03357408568263054</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.2694283127784729</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.06131193786859512</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.07739711552858353</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0.07820554077625275</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0.2943789064884186</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.07408067584037781</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.1349236965179443</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.06513939797878265</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.1816798746585846</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.004942657425999641</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.03348971158266068</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.09539182484149933</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.04907611012458801</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.1667899638414383</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.01934267580509186</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.02774300798773766</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.02695028111338615</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.1182636767625809</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.09704697132110596</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.05054515227675438</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.03790559992194176</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.03934495151042938</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.2616918087005615</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>0.0652976855635643</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>0.1816576272249222</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.06504928320646286</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.1262483596801758</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.05421898141503334</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.008476271294057369</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.01068056374788284</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.03267477452754974</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>0.1519458293914795</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>0.02625739946961403</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.0167983416467905</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.01621695421636105</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.1169331222772598</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.07080757617950439</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.07449931651353836</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.04348553344607353</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.04949406534433365</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.04051320627331734</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.08417847007513046</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.03768104687333107</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0.2865248322486877</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>0.07914216816425323</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>0.02381793409585953</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.05372762680053711</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0.1350554078817368</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.0439046174287796</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>0.1025273352861404</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>0.06600326299667358</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.001244477927684784</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0.03680222481489182</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0.1886427253484726</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0.05029084905982018</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0.1826644688844681</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>0.04404418170452118</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.0772954598069191</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>0.02383363805711269</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>0.04060549661517143</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>0.1238741874694824</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0.1978845149278641</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>0.2008712589740753</v>
+      </c>
+      <c r="EC7" t="n">
+        <v>0.02467255666851997</v>
+      </c>
+      <c r="ED7" t="n">
+        <v>0.0298131387680769</v>
+      </c>
+      <c r="EE7" t="n">
+        <v>0.08564458787441254</v>
+      </c>
+      <c r="EF7" t="n">
+        <v>0.06071893870830536</v>
+      </c>
+      <c r="EG7" t="n">
+        <v>0.01168574020266533</v>
+      </c>
+      <c r="EH7" t="n">
+        <v>0.08583118766546249</v>
+      </c>
+      <c r="EI7" t="n">
+        <v>0.1919248700141907</v>
+      </c>
+      <c r="EJ7" t="n">
+        <v>0.03371670842170715</v>
+      </c>
+      <c r="EK7" t="n">
+        <v>0.06822732836008072</v>
+      </c>
+      <c r="EL7" t="n">
+        <v>0.05797622352838516</v>
+      </c>
+      <c r="EM7" t="n">
+        <v>0.04092766717076302</v>
+      </c>
+      <c r="EN7" t="n">
+        <v>0.04301975667476654</v>
+      </c>
+      <c r="EO7" t="n">
+        <v>0.03534496948122978</v>
+      </c>
+      <c r="EP7" t="n">
+        <v>0.05386785417795181</v>
+      </c>
+      <c r="EQ7" t="n">
+        <v>0.02869018167257309</v>
+      </c>
+      <c r="ER7" t="n">
+        <v>0.03862949088215828</v>
+      </c>
+      <c r="ES7" t="n">
+        <v>0.0309831015765667</v>
+      </c>
+      <c r="ET7" t="n">
+        <v>0.1116878762841225</v>
+      </c>
+      <c r="EU7" t="n">
+        <v>0.02808389812707901</v>
+      </c>
+      <c r="EV7" t="n">
+        <v>0.04697681218385696</v>
+      </c>
+      <c r="EW7" t="n">
+        <v>0.1369953751564026</v>
+      </c>
+      <c r="EX7" t="n">
+        <v>0.04808497428894043</v>
+      </c>
+      <c r="EY7" t="n">
+        <v>0.1864133179187775</v>
+      </c>
+      <c r="EZ7" t="n">
+        <v>0.01179833337664604</v>
+      </c>
+      <c r="FA7" t="n">
+        <v>0.01554118096828461</v>
+      </c>
+      <c r="FB7" t="n">
+        <v>0.03655426204204559</v>
+      </c>
+      <c r="FC7" t="n">
+        <v>0.1073737442493439</v>
+      </c>
+      <c r="FD7" t="n">
+        <v>0.08667010068893433</v>
+      </c>
+      <c r="FE7" t="n">
+        <v>0.07997236400842667</v>
+      </c>
+      <c r="FF7" t="n">
+        <v>0.0133937606588006</v>
+      </c>
+      <c r="FG7" t="n">
+        <v>0.006486129015684128</v>
+      </c>
+      <c r="FH7" t="n">
+        <v>0.2269787788391113</v>
+      </c>
+      <c r="FI7" t="n">
+        <v>0.0989287793636322</v>
+      </c>
+      <c r="FJ7" t="n">
+        <v>0.02362198010087013</v>
+      </c>
+      <c r="FK7" t="n">
+        <v>0.07188330590724945</v>
+      </c>
+      <c r="FL7" t="n">
+        <v>0.1717151552438736</v>
+      </c>
+      <c r="FM7" t="n">
+        <v>0.0728580430150032</v>
+      </c>
+      <c r="FN7" t="n">
+        <v>0.3014926910400391</v>
+      </c>
+      <c r="FO7" t="n">
+        <v>0.01148337218910456</v>
+      </c>
+      <c r="FP7" t="n">
+        <v>0.1199577748775482</v>
+      </c>
+      <c r="FQ7" t="n">
+        <v>0.1653447896242142</v>
+      </c>
+      <c r="FR7" t="n">
+        <v>0.31549271941185</v>
+      </c>
+      <c r="FS7" t="n">
+        <v>0.2112739682197571</v>
+      </c>
+      <c r="FT7" t="n">
+        <v>0.04070359840989113</v>
+      </c>
+      <c r="FU7" t="n">
+        <v>0.1673319637775421</v>
+      </c>
+      <c r="FV7" t="n">
+        <v>0.1272211968898773</v>
+      </c>
+      <c r="FW7" t="n">
+        <v>0.009020671248435974</v>
+      </c>
+      <c r="FX7" t="n">
+        <v>0.0573698952794075</v>
+      </c>
+      <c r="FY7" t="n">
+        <v>0.06356402486562729</v>
+      </c>
+      <c r="FZ7" t="n">
+        <v>0.08357086777687073</v>
+      </c>
+      <c r="GA7" t="n">
+        <v>0.05474743992090225</v>
+      </c>
+      <c r="GB7" t="n">
+        <v>0.08045884966850281</v>
+      </c>
+      <c r="GC7" t="n">
+        <v>0.1602718681097031</v>
+      </c>
+      <c r="GD7" t="n">
+        <v>0.09462413936853409</v>
+      </c>
+      <c r="GE7" t="n">
+        <v>0.01099604927003384</v>
+      </c>
+      <c r="GF7" t="n">
+        <v>0.1268810927867889</v>
+      </c>
+      <c r="GG7" t="n">
+        <v>0.1741521060466766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>0</v>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES8" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>0.0007629734463989735</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0.00177220196928829</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.611996023915708e-05</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.0006025418406352401</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0002068908652290702</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0007638723473064601</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0002188726502936333</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0005286513478495181</v>
+      </c>
+      <c r="I9" t="n">
+        <v>9.848910849541426e-05</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0005722916685044765</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.002006251132115722</v>
+      </c>
+      <c r="L9" t="n">
+        <v>9.937502909451723e-06</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0008455172064714134</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0005874024354852736</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0009779526153579354</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.622113581513986e-06</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0001250725472345948</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.0006067976355552673</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.000185979763045907</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.937328099505976e-05</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.0001384003553539515</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.0002357700432185084</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.0003824268933385611</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.0003056642890442163</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.0002639661252032965</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.0003930367238353938</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.08908773958683e-05</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.301439184928313e-05</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.811519703362137e-05</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.0001669572957325727</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.000608972564805299</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.0008286595111712813</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.0004016751772724092</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.0001123383481171913</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.0005691516562364995</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>4.140533928875811e-05</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0.0002819376531988382</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.0003527552762534469</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.000260835891822353</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0.0002699144533835351</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>6.719148950651288e-05</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.0001815916039049625</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.000355593248968944</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.0001668922195676714</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.084705430315807e-05</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.0004530146543402225</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.00126093509607017</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.0003016234550159425</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>4.579878805088811e-05</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.001023094984702766</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.0005960070993751287</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>2.96827893180307e-05</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0.0002250415127491578</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.0002316118043381721</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0.0002585994952823967</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0.0003508251393213868</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.0001757502759573981</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0.000350659538526088</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0.0006165498052723706</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>8.33834201330319e-05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>5.948445505055133e-06</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.0002614122349768877</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.0001260706631001085</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>5.984612289466895e-05</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.0002025280409725383</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>7.655335502931848e-05</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>4.948690548189916e-05</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0003128382377326488</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>4.713303496828303e-06</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.0004589098680298775</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.0002061183913610876</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.0003447017224971205</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.0003873224777635187</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.0007764273905195296</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.000155297908349894</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0001054395470418967</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.0002416234492557123</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.000620383070781827</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0003013044770341367</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>7.612027548020706e-05</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.0001081932277884334</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>0.0001414129073964432</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.0005395006737671793</v>
+      </c>
+      <c r="CF9" t="n">
+        <v>5.801796214655042e-05</v>
+      </c>
+      <c r="CG9" t="n">
+        <v>0.0001565752463648096</v>
+      </c>
+      <c r="CH9" t="n">
+        <v>0.0001228122127940878</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.0002535006788093597</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.0001009046754916199</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>9.49978712014854e-05</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>0.0001531135494587943</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>0.0003470983938314021</v>
+      </c>
+      <c r="CN9" t="n">
+        <v>0.0006783746648579836</v>
+      </c>
+      <c r="CO9" t="n">
+        <v>0.0004688266781158745</v>
+      </c>
+      <c r="CP9" t="n">
+        <v>0.0002971089270431548</v>
+      </c>
+      <c r="CQ9" t="n">
+        <v>7.818576705176383e-05</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>0.0004420941113494337</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>6.165054219309241e-05</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>0.0001284370810026303</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>0.000173832886503078</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>8.631550008431077e-05</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>0.0005002962425351143</v>
+      </c>
+      <c r="CX9" t="n">
+        <v>4.07727638958022e-05</v>
+      </c>
+      <c r="CY9" t="n">
+        <v>0.0001798174635041505</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>0.0001202740240842104</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>0.0002699918404687196</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>6.87142619426595e-06</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0.000214670755667612</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>0.0001135450147558004</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>0.0001856433664215729</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>0.0001316818379564211</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0.0001371244870824739</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>0.0002194053522543982</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>0.0006692958995699883</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>4.843101487495005e-05</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>0.0002120673307217658</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>9.098916780203581e-05</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>1.9106111722067e-05</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>0.0001417263993062079</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>0.0003629322454798967</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>0.0001722514571156353</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>3.925464625353925e-05</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.0002485828008502722</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0.0001641139679122716</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>0.0001847063249442726</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0.0003488562360871583</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>0.0001899090566439554</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>0.0002105389867210761</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>0.0002677598386071622</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>0.0002619692531879991</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.0002606413327157497</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>0.0001281904405914247</v>
+      </c>
+      <c r="EB9" t="n">
+        <v>1.008488470688462e-05</v>
+      </c>
+      <c r="EC9" t="n">
+        <v>1.099066321330611e-05</v>
+      </c>
+      <c r="ED9" t="n">
+        <v>0.0002998725976794958</v>
+      </c>
+      <c r="EE9" t="n">
+        <v>0.0002155016845790669</v>
+      </c>
+      <c r="EF9" t="n">
+        <v>4.691218782681972e-05</v>
+      </c>
+      <c r="EG9" t="n">
+        <v>6.349370232783258e-05</v>
+      </c>
+      <c r="EH9" t="n">
+        <v>0.0002837373758666217</v>
+      </c>
+      <c r="EI9" t="n">
+        <v>1.188856731459964e-05</v>
+      </c>
+      <c r="EJ9" t="n">
+        <v>2.429921732982621e-05</v>
+      </c>
+      <c r="EK9" t="n">
+        <v>0.0001388503151247278</v>
+      </c>
+      <c r="EL9" t="n">
+        <v>4.8824349505594e-05</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.0001749618968460709</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>6.132180715212598e-05</v>
+      </c>
+      <c r="EO9" t="n">
+        <v>0.0002522533759474754</v>
+      </c>
+      <c r="EP9" t="n">
+        <v>0.0002524120209272951</v>
+      </c>
+      <c r="EQ9" t="n">
+        <v>0.0001009774714475498</v>
+      </c>
+      <c r="ER9" t="n">
+        <v>3.32269883074332e-05</v>
+      </c>
+      <c r="ES9" t="n">
+        <v>0.0001832339621614665</v>
+      </c>
+      <c r="ET9" t="n">
+        <v>0.0003832883085124195</v>
+      </c>
+      <c r="EU9" t="n">
+        <v>0.0001239505800185725</v>
+      </c>
+      <c r="EV9" t="n">
+        <v>8.809153223410249e-05</v>
+      </c>
+      <c r="EW9" t="n">
+        <v>0.0002281933702761307</v>
+      </c>
+      <c r="EX9" t="n">
+        <v>0.0001333531690761447</v>
+      </c>
+      <c r="EY9" t="n">
+        <v>0.0005869177985005081</v>
+      </c>
+      <c r="EZ9" t="n">
+        <v>3.74637747881934e-05</v>
+      </c>
+      <c r="FA9" t="n">
+        <v>0.0001809802633943036</v>
+      </c>
+      <c r="FB9" t="n">
+        <v>6.386158929672092e-05</v>
+      </c>
+      <c r="FC9" t="n">
+        <v>0.000210071200854145</v>
+      </c>
+      <c r="FD9" t="n">
+        <v>0.0001051300641847774</v>
+      </c>
+      <c r="FE9" t="n">
+        <v>0.0001388991804560646</v>
+      </c>
+      <c r="FF9" t="n">
+        <v>2.043839049292728e-05</v>
+      </c>
+      <c r="FG9" t="n">
+        <v>1.416507620888297e-05</v>
+      </c>
+      <c r="FH9" t="n">
+        <v>0.0003267602878622711</v>
+      </c>
+      <c r="FI9" t="n">
+        <v>0.0002831430756486952</v>
+      </c>
+      <c r="FJ9" t="n">
+        <v>0.0002274074940942228</v>
+      </c>
+      <c r="FK9" t="n">
+        <v>4.162126424489543e-05</v>
+      </c>
+      <c r="FL9" t="n">
+        <v>0.0004448334220796824</v>
+      </c>
+      <c r="FM9" t="n">
+        <v>0.0001943603274412453</v>
+      </c>
+      <c r="FN9" t="n">
+        <v>0.0002552726655267179</v>
+      </c>
+      <c r="FO9" t="n">
+        <v>0.0004037919570691884</v>
+      </c>
+      <c r="FP9" t="n">
+        <v>0.0005751359276473522</v>
+      </c>
+      <c r="FQ9" t="n">
+        <v>0.0006584866787306964</v>
+      </c>
+      <c r="FR9" t="n">
+        <v>0.0004184726858511567</v>
+      </c>
+      <c r="FS9" t="n">
+        <v>0.0003949407255277038</v>
+      </c>
+      <c r="FT9" t="n">
+        <v>0.0001284511818084866</v>
+      </c>
+      <c r="FU9" t="n">
+        <v>0.0004425978695508093</v>
+      </c>
+      <c r="FV9" t="n">
+        <v>0.0003071076353080571</v>
+      </c>
+      <c r="FW9" t="n">
+        <v>0.0001594891946297139</v>
+      </c>
+      <c r="FX9" t="n">
+        <v>0.0001217587414430454</v>
+      </c>
+      <c r="FY9" t="n">
+        <v>0.000134914880618453</v>
+      </c>
+      <c r="FZ9" t="n">
+        <v>4.137687938055024e-05</v>
+      </c>
+      <c r="GA9" t="n">
+        <v>0.0003051798557862639</v>
+      </c>
+      <c r="GB9" t="n">
+        <v>9.618915646569803e-05</v>
+      </c>
+      <c r="GC9" t="n">
+        <v>0.0002593026147224009</v>
+      </c>
+      <c r="GD9" t="n">
+        <v>0.0004183637211099267</v>
+      </c>
+      <c r="GE9" t="n">
+        <v>0.0003032485547009856</v>
+      </c>
+      <c r="GF9" t="n">
+        <v>0.0002216503780800849</v>
+      </c>
+      <c r="GG9" t="n">
+        <v>0.0001592128537595272</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES10" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>0.009222419932484627</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.02772746607661247</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.007974687032401562</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.006798240356147289</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01049359794706106</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.06395919620990753</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.031198866665363e-05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.05854961276054382</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01011574454605579</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.007372251711785793</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02615086361765862</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.538548480719328e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01626338623464108</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.002383984625339508</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05911187827587128</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.007807817310094833</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.06866269558668137</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.02239051833748817</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.002061107195913792</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.01052237488329411</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.002568782772868872</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.01208600308746099</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.007579706609249115</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.001368347555398941</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.0009519579471088946</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.005416144616901875</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.001705854199826717</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.002802903763949871</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.00363279739394784</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.002545003779232502</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.02672994136810303</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.03332646936178207</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.001787178916856647</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.0183442123234272</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.005619203206151724</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.01030902378261089</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.003957826644182205</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.0115150036290288</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.008513427339494228</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>9.142700582742691e-05</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.02254359982907772</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.02615381591022015</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.007732819765806198</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.004565537441521883</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0.00531469751149416</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.001056522829458117</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.07052130997180939</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0.005783817265182734</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0.003216428216546774</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0.02476931363344193</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0.0265013612806797</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.005641847848892212</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0.001788558438420296</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>0.02001837827265263</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>0.003928635735064745</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>0.04928036034107208</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>0.01481120567768812</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0.007050689309835434</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>0.0623241625726223</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.01265390962362289</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.003968081902712584</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.006368522066622972</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.0001595877110958099</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.006725326180458069</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.0008754506707191467</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>0.0182916671037674</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>0.0032705282792449</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>0.00621067825704813</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>0.006977979559451342</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>0.004159459844231606</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>0.01273305248469114</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>0.001139529282227159</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>0.0005704211071133614</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>0.03201258927583694</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>0.00111167156137526</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>0.006058790255337954</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>0.01485080644488335</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>0.02306396141648293</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>0.007211664225906134</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>0.004244681913405657</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.0001781936298357323</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.001388825592584908</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.01147702801972628</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.009526785463094711</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.004945926833897829</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.002713412046432495</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.01690447330474854</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.002345873508602381</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.01278611551970243</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>0.004399081692099571</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>0.003577916650101542</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>0.004715984221547842</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>0.01452290080487728</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>0.02474383451044559</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>0.05596921592950821</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>0.008236228488385677</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>0.009126357734203339</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>0.02178654074668884</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>0.003216606797650456</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>0.001872979803010821</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>0.008565636351704597</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>0.007354838773608208</v>
+      </c>
+      <c r="CY11" t="n">
+        <v>0.00344506767578423</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>0.002097365446388721</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>0.01773645356297493</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>0.001030383515171707</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0.007941165007650852</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>0.003037883201614022</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.0172384437173605</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>0.01865711249411106</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0.01045473851263523</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>0.01788242533802986</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0.02135336026549339</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>0.008814599364995956</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>0.01466122828423977</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.003501153085380793</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>0.03403618931770325</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.006863247137516737</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>0.005588694475591183</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>0.001856289571151137</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0.00910966657102108</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0.003115951316431165</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0.009837066754698753</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.005723298061639071</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.004295177757740021</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>0.001701157074421644</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.0006385312881320715</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>0.001240236451849341</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>0.01538232434540987</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>0.01432526297867298</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>0.005839656572788954</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>0.002250673482194543</v>
+      </c>
+      <c r="EC11" t="n">
+        <v>0.005433423910290003</v>
+      </c>
+      <c r="ED11" t="n">
+        <v>0.006189970299601555</v>
+      </c>
+      <c r="EE11" t="n">
+        <v>0.018645990639925</v>
+      </c>
+      <c r="EF11" t="n">
+        <v>0.002802302362397313</v>
+      </c>
+      <c r="EG11" t="n">
+        <v>0.001102661015465856</v>
+      </c>
+      <c r="EH11" t="n">
+        <v>0.004340783692896366</v>
+      </c>
+      <c r="EI11" t="n">
+        <v>0.007064762525260448</v>
+      </c>
+      <c r="EJ11" t="n">
+        <v>0.008022572845220566</v>
+      </c>
+      <c r="EK11" t="n">
+        <v>0.001981615554541349</v>
+      </c>
+      <c r="EL11" t="n">
+        <v>0.01062601990997791</v>
+      </c>
+      <c r="EM11" t="n">
+        <v>0.01209063827991486</v>
+      </c>
+      <c r="EN11" t="n">
+        <v>0.00418354757130146</v>
+      </c>
+      <c r="EO11" t="n">
+        <v>0.004161856137216091</v>
+      </c>
+      <c r="EP11" t="n">
+        <v>0.01752704381942749</v>
+      </c>
+      <c r="EQ11" t="n">
+        <v>0.0005907129961997271</v>
+      </c>
+      <c r="ER11" t="n">
+        <v>0.005729008000344038</v>
+      </c>
+      <c r="ES11" t="n">
+        <v>0.01071131229400635</v>
+      </c>
+      <c r="ET11" t="n">
+        <v>0.01938809081912041</v>
+      </c>
+      <c r="EU11" t="n">
+        <v>0.02310717292129993</v>
+      </c>
+      <c r="EV11" t="n">
+        <v>0.009234133176505566</v>
+      </c>
+      <c r="EW11" t="n">
+        <v>0.0126497708261013</v>
+      </c>
+      <c r="EX11" t="n">
+        <v>0.0001506069675087929</v>
+      </c>
+      <c r="EY11" t="n">
+        <v>0.01247144490480423</v>
+      </c>
+      <c r="EZ11" t="n">
+        <v>0.007352849934250116</v>
+      </c>
+      <c r="FA11" t="n">
+        <v>0.002803022274747491</v>
+      </c>
+      <c r="FB11" t="n">
+        <v>0.0009348634630441666</v>
+      </c>
+      <c r="FC11" t="n">
+        <v>0.01473468169569969</v>
+      </c>
+      <c r="FD11" t="n">
+        <v>0.001388208824209869</v>
+      </c>
+      <c r="FE11" t="n">
+        <v>0.009653165005147457</v>
+      </c>
+      <c r="FF11" t="n">
+        <v>0.0004549087025225163</v>
+      </c>
+      <c r="FG11" t="n">
+        <v>0.003286421298980713</v>
+      </c>
+      <c r="FH11" t="n">
+        <v>0.01662997156381607</v>
+      </c>
+      <c r="FI11" t="n">
+        <v>0.002985831815749407</v>
+      </c>
+      <c r="FJ11" t="n">
+        <v>0.006322650238871574</v>
+      </c>
+      <c r="FK11" t="n">
+        <v>0.003627795726060867</v>
+      </c>
+      <c r="FL11" t="n">
+        <v>0.02054766565561295</v>
+      </c>
+      <c r="FM11" t="n">
+        <v>0.004571741446852684</v>
+      </c>
+      <c r="FN11" t="n">
+        <v>0.00290606077760458</v>
+      </c>
+      <c r="FO11" t="n">
+        <v>0.002379664452746511</v>
+      </c>
+      <c r="FP11" t="n">
+        <v>0.0004798187874257565</v>
+      </c>
+      <c r="FQ11" t="n">
+        <v>0.03345280885696411</v>
+      </c>
+      <c r="FR11" t="n">
+        <v>0.05433777719736099</v>
+      </c>
+      <c r="FS11" t="n">
+        <v>0.0163189135491848</v>
+      </c>
+      <c r="FT11" t="n">
+        <v>0.01139320619404316</v>
+      </c>
+      <c r="FU11" t="n">
+        <v>0.02582145482301712</v>
+      </c>
+      <c r="FV11" t="n">
+        <v>0.01860788464546204</v>
+      </c>
+      <c r="FW11" t="n">
+        <v>0.00406405795365572</v>
+      </c>
+      <c r="FX11" t="n">
+        <v>0.03201614692807198</v>
+      </c>
+      <c r="FY11" t="n">
+        <v>0.01127292308956385</v>
+      </c>
+      <c r="FZ11" t="n">
+        <v>0.007311198394745588</v>
+      </c>
+      <c r="GA11" t="n">
+        <v>0.003222510684281588</v>
+      </c>
+      <c r="GB11" t="n">
+        <v>0.005533637013286352</v>
+      </c>
+      <c r="GC11" t="n">
+        <v>0.01072562858462334</v>
+      </c>
+      <c r="GD11" t="n">
+        <v>0.003233876544982195</v>
+      </c>
+      <c r="GE11" t="n">
+        <v>0.002729051746428013</v>
+      </c>
+      <c r="GF11" t="n">
+        <v>0.01357007492333651</v>
+      </c>
+      <c r="GG11" t="n">
+        <v>0.006572984624654055</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2.260931353248452e-07</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1.331552448391449e-05</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.558016371447593e-06</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2.431205757602584e-06</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.362344614288304e-06</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.262926070921822e-05</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.433524801086605e-07</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.020305019977968e-06</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.647517819947097e-06</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6.626797812714358e-07</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.667788274062332e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.242801984830294e-06</v>
+      </c>
+      <c r="M12" t="n">
+        <v>5.073819920653477e-06</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.63775438927405e-06</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.297240214626072e-05</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.349305421172176e-06</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.919737304793671e-06</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.518613771622768e-06</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.316235392958333e-07</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.215875045090797e-06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.26624672197795e-07</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.977030024136184e-06</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.284096697418136e-06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.44175566371996e-06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.039042558659276e-06</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.26633392230724e-06</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.522977749526035e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.014679696709209e-06</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.526429969089804e-06</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.285577809539973e-06</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.653689309932815e-06</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.413643298699753e-06</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>2.809231091305264e-06</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>9.899447377392789e-07</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>6.528372978209518e-06</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.580515231580648e-06</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.090080786525505e-06</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3.673269475257257e-06</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>7.139371973607922e-07</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>2.460374616930494e-06</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>5.629362931358628e-07</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.910218998091295e-06</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.367341380704602e-07</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.836650310200639e-06</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.840398113017727e-06</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>2.209565536759328e-06</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.617762973182835e-05</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.984474693017546e-06</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>2.363461135246325e-06</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>7.162765996326925e-06</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.092700586013962e-05</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4.119445122796606e-07</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.65938445206848e-06</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.791357135516591e-06</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>7.492167242162395e-07</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>3.949407073378097e-06</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.256077889091102e-06</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>3.063104259126703e-08</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>5.038161361881066e-06</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>9.843749921856215e-07</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>2.185382982133888e-06</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.804295038709824e-06</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>2.381055310252123e-06</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>8.518679806002183e-07</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>1.702526105873403e-06</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>8.87111809788621e-07</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>9.896166375256144e-08</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>6.738988531651557e-07</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>8.190272637875751e-07</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>9.229643183061853e-08</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>2.811405579450366e-07</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>1.226532504006173e-06</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>6.262236524889886e-07</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>8.099232218228281e-06</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>7.735185363344499e-07</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>2.49029517362942e-06</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>2.977624944833224e-06</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>7.437586646119598e-06</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>2.010673142649466e-06</v>
+      </c>
+      <c r="CB12" t="n">
+        <v>1.830283736126148e-06</v>
+      </c>
+      <c r="CC12" t="n">
+        <v>2.539316881211562e-07</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>2.49971492394252e-07</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>4.89852754981257e-06</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>8.813577778710169e-07</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>1.393029947394098e-06</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>2.967485670524184e-07</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>2.871531933124061e-06</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>2.203675819600903e-08</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.460375983697304e-06</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>4.258570811543905e-07</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1.265629180124961e-06</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>3.459154186202795e-06</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>3.487252115519368e-06</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>3.571040906535927e-06</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>4.621063908416545e-06</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>2.373261168031604e-06</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>3.928930709662382e-07</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>3.009596412084647e-07</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.520613523098291e-06</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>5.843663188898063e-07</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>4.242383511154912e-06</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>1.534616785647813e-06</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>2.053592197626131e-06</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>6.728021730850742e-07</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>3.384221372471075e-06</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>4.608366737102187e-07</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>1.099980181606952e-06</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>7.562965720353532e-08</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>1.267740685761964e-07</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>3.335003384563606e-06</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>1.710842411739577e-06</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>8.002647291505127e-07</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>3.551250529199024e-07</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>5.31475234311074e-06</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>8.262026653937937e-07</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>5.377513843995985e-06</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>1.959539758900064e-06</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>1.048429339789436e-06</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>1.693845547379169e-06</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>7.977378118084744e-07</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>4.264438189238717e-07</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>4.738421068850585e-07</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>2.544878043408971e-06</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>1.90389471299568e-06</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>3.090172867814545e-06</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>2.940561216746573e-07</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>2.290335487487027e-06</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>2.506821147107985e-06</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>2.653389628903824e-06</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>4.839766916120425e-07</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>2.777258032438112e-06</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>3.406401447136886e-06</v>
+      </c>
+      <c r="EC12" t="n">
+        <v>1.53622715970414e-06</v>
+      </c>
+      <c r="ED12" t="n">
+        <v>4.213711690681521e-06</v>
+      </c>
+      <c r="EE12" t="n">
+        <v>3.523523673720774e-06</v>
+      </c>
+      <c r="EF12" t="n">
+        <v>9.60421175477677e-07</v>
+      </c>
+      <c r="EG12" t="n">
+        <v>2.282399236719357e-06</v>
+      </c>
+      <c r="EH12" t="n">
+        <v>3.996466375610908e-07</v>
+      </c>
+      <c r="EI12" t="n">
+        <v>3.175789515807992e-07</v>
+      </c>
+      <c r="EJ12" t="n">
+        <v>1.117591637012083e-06</v>
+      </c>
+      <c r="EK12" t="n">
+        <v>1.081042455552961e-06</v>
+      </c>
+      <c r="EL12" t="n">
+        <v>6.433809858208406e-07</v>
+      </c>
+      <c r="EM12" t="n">
+        <v>8.796274642008939e-07</v>
+      </c>
+      <c r="EN12" t="n">
+        <v>4.239961413077253e-07</v>
+      </c>
+      <c r="EO12" t="n">
+        <v>1.320699993812013e-06</v>
+      </c>
+      <c r="EP12" t="n">
+        <v>2.173077973566251e-06</v>
+      </c>
+      <c r="EQ12" t="n">
+        <v>2.747973155692307e-07</v>
+      </c>
+      <c r="ER12" t="n">
+        <v>2.780574277494452e-06</v>
+      </c>
+      <c r="ES12" t="n">
+        <v>1.776833983058168e-06</v>
+      </c>
+      <c r="ET12" t="n">
+        <v>3.509604766804841e-07</v>
+      </c>
+      <c r="EU12" t="n">
+        <v>2.493594308816682e-07</v>
+      </c>
+      <c r="EV12" t="n">
+        <v>1.06904951735487e-06</v>
+      </c>
+      <c r="EW12" t="n">
+        <v>2.267814579681726e-06</v>
+      </c>
+      <c r="EX12" t="n">
+        <v>2.003773715841817e-07</v>
+      </c>
+      <c r="EY12" t="n">
+        <v>5.260483703750651e-06</v>
+      </c>
+      <c r="EZ12" t="n">
+        <v>1.085372559828102e-06</v>
+      </c>
+      <c r="FA12" t="n">
+        <v>1.692385694695986e-06</v>
+      </c>
+      <c r="FB12" t="n">
+        <v>1.192740910482826e-07</v>
+      </c>
+      <c r="FC12" t="n">
+        <v>3.491861434667953e-06</v>
+      </c>
+      <c r="FD12" t="n">
+        <v>2.178035174438264e-07</v>
+      </c>
+      <c r="FE12" t="n">
+        <v>1.438602453163185e-06</v>
+      </c>
+      <c r="FF12" t="n">
+        <v>5.569600602939317e-07</v>
+      </c>
+      <c r="FG12" t="n">
+        <v>7.841179581191682e-07</v>
+      </c>
+      <c r="FH12" t="n">
+        <v>3.041574018425308e-06</v>
+      </c>
+      <c r="FI12" t="n">
+        <v>1.511372488494089e-06</v>
+      </c>
+      <c r="FJ12" t="n">
+        <v>1.100509734897059e-06</v>
+      </c>
+      <c r="FK12" t="n">
+        <v>1.351924652226444e-06</v>
+      </c>
+      <c r="FL12" t="n">
+        <v>1.857382471825986e-06</v>
+      </c>
+      <c r="FM12" t="n">
+        <v>6.811861794631113e-07</v>
+      </c>
+      <c r="FN12" t="n">
+        <v>4.005195023637498e-06</v>
+      </c>
+      <c r="FO12" t="n">
+        <v>4.138772055739537e-06</v>
+      </c>
+      <c r="FP12" t="n">
+        <v>1.168863605016668e-06</v>
+      </c>
+      <c r="FQ12" t="n">
+        <v>2.10217444873706e-06</v>
+      </c>
+      <c r="FR12" t="n">
+        <v>3.591263521229848e-06</v>
+      </c>
+      <c r="FS12" t="n">
+        <v>6.758764925507421e-07</v>
+      </c>
+      <c r="FT12" t="n">
+        <v>1.416214217897505e-06</v>
+      </c>
+      <c r="FU12" t="n">
+        <v>1.957585482159629e-06</v>
+      </c>
+      <c r="FV12" t="n">
+        <v>3.579546500986908e-06</v>
+      </c>
+      <c r="FW12" t="n">
+        <v>5.446495379146654e-06</v>
+      </c>
+      <c r="FX12" t="n">
+        <v>3.615700734371785e-06</v>
+      </c>
+      <c r="FY12" t="n">
+        <v>1.355455424345564e-06</v>
+      </c>
+      <c r="FZ12" t="n">
+        <v>1.922843324564383e-07</v>
+      </c>
+      <c r="GA12" t="n">
+        <v>4.236574113747338e-06</v>
+      </c>
+      <c r="GB12" t="n">
+        <v>4.06930439567077e-07</v>
+      </c>
+      <c r="GC12" t="n">
+        <v>5.112958206154872e-06</v>
+      </c>
+      <c r="GD12" t="n">
+        <v>3.121262807326275e-06</v>
+      </c>
+      <c r="GE12" t="n">
+        <v>1.178090769826667e-06</v>
+      </c>
+      <c r="GF12" t="n">
+        <v>1.274019041375141e-06</v>
+      </c>
+      <c r="GG12" t="n">
+        <v>1.460632574890042e-06</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>0.0136986505240202</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.3464870452880859</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.2575156688690186</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.04943093657493591</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.01082101557403803</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0981266051530838</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1257601231336594</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.08529955148696899</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1922573745250702</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.000111081637442112</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.3793814480304718</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.345160961151123</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.004718683660030365</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.03275381773710251</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01815280690789223</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.1305083781480789</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.04426627606153488</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.1102370321750641</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.001653965562582016</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.03576590493321419</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.0306207612156868</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.008015796542167664</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.01177477650344372</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1426209062337875</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.007011487148702145</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.01876341179013252</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.09973825514316559</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.09743092954158783</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0.06654678285121918</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.04201720654964447</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0.1663561016321182</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.2149706780910492</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0.07614800333976746</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0.06929848343133926</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.02213412709534168</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.1224918514490128</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.02802983671426773</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0.1108639389276505</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.03670937567949295</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0.03381713107228279</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.1163924485445023</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0.1134324967861176</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0.009732074104249477</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.0612480640411377</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0.003157644532620907</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.007877685129642487</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.2147938758134842</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.01872374676167965</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.07524547725915909</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0.08364497125148773</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0.1609369218349457</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.03589814156293869</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0.08331718295812607</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>0.1116049587726593</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>0.04983358457684517</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>0.005919836927205324</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>0.1246616542339325</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0.04654022678732872</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>0.00775325670838356</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>0.05380164831876755</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>0.09357128292322159</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.06854234635829926</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.01932230778038502</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.007911691442131996</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.06478219479322433</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.03496665507555008</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>0.1342315077781677</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>0.01541707944124937</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>0.02205254882574081</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>0.06368828564882278</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>0.02686029858887196</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>0.03360636532306671</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>0.003690091194584966</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>0.08883911371231079</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0.08614608645439148</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>0.005947823636233807</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>0.07579658180475235</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0.1606779098510742</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0.03752823919057846</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>0.03055553697049618</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.09009750187397003</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.001945413067005575</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.1388699114322662</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.07822790741920471</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>0.0007097236812114716</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.01400056947022676</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>0.006390862632542849</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.009523911401629448</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.02462328784167767</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>0.02546298503875732</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>0.01743413880467415</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>0.09929920732975006</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>0.1230030283331871</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>0.1085725054144859</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>0.1240187734365463</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>0.1944096088409424</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>0.004786662757396698</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>0.03604692220687866</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>0.05388883128762245</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>0.01436227187514305</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>0.1296625435352325</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>0.08587180078029633</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>0.0007446333765983582</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>0.003250572830438614</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>0.01608467847108841</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>0.02385983988642693</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.02005804516375065</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.05535654351115227</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.04414927586913109</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>0.1277686953544617</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0.1161118447780609</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.0126882204785943</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0.1653074473142624</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.03303053975105286</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>0.0004834001883864403</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.05250348895788193</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>0.1360196173191071</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.05533610656857491</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>0.01806806027889252</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>0.08333410322666168</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.0530519001185894</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.06048980355262756</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.01142736524343491</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.01069048885256052</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.006108535453677177</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>0.08080445230007172</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.02716589719057083</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>0.05457133799791336</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>0.08310450613498688</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.01070468779653311</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.01827224902808666</v>
+      </c>
+      <c r="EB13" t="n">
+        <v>0.1247848123311996</v>
+      </c>
+      <c r="EC13" t="n">
+        <v>0.006306820549070835</v>
+      </c>
+      <c r="ED13" t="n">
+        <v>0.06082449108362198</v>
+      </c>
+      <c r="EE13" t="n">
+        <v>0.03007007576525211</v>
+      </c>
+      <c r="EF13" t="n">
+        <v>0.008005999028682709</v>
+      </c>
+      <c r="EG13" t="n">
+        <v>0.180731326341629</v>
+      </c>
+      <c r="EH13" t="n">
+        <v>0.01758157275617123</v>
+      </c>
+      <c r="EI13" t="n">
+        <v>0.01783119887113571</v>
+      </c>
+      <c r="EJ13" t="n">
+        <v>0.05117902904748917</v>
+      </c>
+      <c r="EK13" t="n">
+        <v>0.08339287340641022</v>
+      </c>
+      <c r="EL13" t="n">
+        <v>0.000844866968691349</v>
+      </c>
+      <c r="EM13" t="n">
+        <v>0.005818773526698351</v>
+      </c>
+      <c r="EN13" t="n">
+        <v>0.06861163675785065</v>
+      </c>
+      <c r="EO13" t="n">
+        <v>0.02688621357083321</v>
+      </c>
+      <c r="EP13" t="n">
+        <v>0.05951058492064476</v>
+      </c>
+      <c r="EQ13" t="n">
+        <v>0.02234211564064026</v>
+      </c>
+      <c r="ER13" t="n">
+        <v>0.04319552332162857</v>
+      </c>
+      <c r="ES13" t="n">
+        <v>0.01848537288606167</v>
+      </c>
+      <c r="ET13" t="n">
+        <v>0.007245788350701332</v>
+      </c>
+      <c r="EU13" t="n">
+        <v>0.04429398477077484</v>
+      </c>
+      <c r="EV13" t="n">
+        <v>0.04471209645271301</v>
+      </c>
+      <c r="EW13" t="n">
+        <v>0.03879892453551292</v>
+      </c>
+      <c r="EX13" t="n">
+        <v>0.0009851763024926186</v>
+      </c>
+      <c r="EY13" t="n">
+        <v>0.1494321525096893</v>
+      </c>
+      <c r="EZ13" t="n">
+        <v>0.0815703496336937</v>
+      </c>
+      <c r="FA13" t="n">
+        <v>0.01174643635749817</v>
+      </c>
+      <c r="FB13" t="n">
+        <v>0.01655135490000248</v>
+      </c>
+      <c r="FC13" t="n">
+        <v>0.01880000904202461</v>
+      </c>
+      <c r="FD13" t="n">
+        <v>0.01223922614008188</v>
+      </c>
+      <c r="FE13" t="n">
+        <v>0.02202200703322887</v>
+      </c>
+      <c r="FF13" t="n">
+        <v>0.04290580749511719</v>
+      </c>
+      <c r="FG13" t="n">
+        <v>0.009175930172204971</v>
+      </c>
+      <c r="FH13" t="n">
+        <v>0.1119603663682938</v>
+      </c>
+      <c r="FI13" t="n">
+        <v>0.007827792316675186</v>
+      </c>
+      <c r="FJ13" t="n">
+        <v>0.01032365672290325</v>
+      </c>
+      <c r="FK13" t="n">
+        <v>0.05114685744047165</v>
+      </c>
+      <c r="FL13" t="n">
+        <v>0.004392616450786591</v>
+      </c>
+      <c r="FM13" t="n">
+        <v>0.004336036276072264</v>
+      </c>
+      <c r="FN13" t="n">
+        <v>0.007755691651254892</v>
+      </c>
+      <c r="FO13" t="n">
+        <v>0.1038503348827362</v>
+      </c>
+      <c r="FP13" t="n">
+        <v>0.06939823925495148</v>
+      </c>
+      <c r="FQ13" t="n">
+        <v>0.119208924472332</v>
+      </c>
+      <c r="FR13" t="n">
+        <v>0.02654722332954407</v>
+      </c>
+      <c r="FS13" t="n">
+        <v>0.05492714792490005</v>
+      </c>
+      <c r="FT13" t="n">
+        <v>0.124022513628006</v>
+      </c>
+      <c r="FU13" t="n">
+        <v>0.07842952758073807</v>
+      </c>
+      <c r="FV13" t="n">
+        <v>0.01061981730163097</v>
+      </c>
+      <c r="FW13" t="n">
+        <v>0.1247747987508774</v>
+      </c>
+      <c r="FX13" t="n">
+        <v>0.07082423567771912</v>
+      </c>
+      <c r="FY13" t="n">
+        <v>0.0231228731572628</v>
+      </c>
+      <c r="FZ13" t="n">
+        <v>0.1286181509494781</v>
+      </c>
+      <c r="GA13" t="n">
+        <v>0.1148901209235191</v>
+      </c>
+      <c r="GB13" t="n">
+        <v>0.01477313879877329</v>
+      </c>
+      <c r="GC13" t="n">
+        <v>0.05530894547700882</v>
+      </c>
+      <c r="GD13" t="n">
+        <v>0.0156533382833004</v>
+      </c>
+      <c r="GE13" t="n">
+        <v>0.06194386258721352</v>
+      </c>
+      <c r="GF13" t="n">
+        <v>0.08779048919677734</v>
+      </c>
+      <c r="GG13" t="n">
+        <v>0.04991176724433899</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1.036001776810735e-05</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.001746461843140423</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.0003518226440064609</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0007433837163262069</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.0009156743763014674</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.002103458158671856</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.001028895610943437</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.001566906576044858</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.0008262447081506252</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.202036557719111e-05</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.002219885354861617</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0001962388050742447</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.001230951165780425</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.001655847649089992</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.002839152934029698</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.0006586455274373293</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.0006886128685437143</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.0008854327024891973</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5.936237721471116e-05</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.231816274113953e-05</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0004720276338048279</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.0003134458675049245</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.0003708401054609567</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0003953843552153558</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.0002606168563943356</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.0009652636363171041</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.0002413225010968745</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.0002543895971029997</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.0001360605529043823</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.631955819902942e-05</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0.0006156438612379134</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0.0008873328333720565</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0.0005315060261636972</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>7.070956053212285e-05</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.001581560587510467</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>4.234505468048155e-05</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0001791848335415125</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0.0001228189212270081</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.0001996789796976373</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0.0002969082852359861</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.0004126093990635127</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0.0003088940284214914</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.0001895013556350023</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.001045714481733739</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.576367741217837e-05</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0.0004632315249182284</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.002183723263442516</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.0002105117018800229</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.0003938949375879019</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0.001093837083317339</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0.001648316741921008</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>8.425729174632579e-05</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0.000448258186224848</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>0.0002209043013863266</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>8.36151884868741e-05</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>0.00054876011563465</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.210375042632222e-05</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0.0009215734899044037</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>0.0005324357771314681</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.502892160322517e-05</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>0.0002793062303680927</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.001373885432258248</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.0004821739858016372</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>9.293832408729941e-05</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.0007486207177862525</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>0.0001058871202985756</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>0.0002367385022807866</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>0.0006284902337938547</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>6.38064811937511e-05</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>0.00120222067926079</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>0.0005808973801322281</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>0.0002527931064832956</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>0.0001351318787783384</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>0.000966354738920927</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>0.0002843527472577989</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>0.0004520517541095614</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>0.0003667275886982679</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0.0007763864705339074</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0.0001748012145981193</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>0.000318027101457119</v>
+      </c>
+      <c r="CC14" t="n">
+        <v>0.000126188897411339</v>
+      </c>
+      <c r="CD14" t="n">
+        <v>4.224343865644187e-05</v>
+      </c>
+      <c r="CE14" t="n">
+        <v>0.0004761133750434965</v>
+      </c>
+      <c r="CF14" t="n">
+        <v>1.694183811196126e-05</v>
+      </c>
+      <c r="CG14" t="n">
+        <v>0.0002856931532733142</v>
+      </c>
+      <c r="CH14" t="n">
+        <v>0.0003426518524065614</v>
+      </c>
+      <c r="CI14" t="n">
+        <v>0.0006427736952900887</v>
+      </c>
+      <c r="CJ14" t="n">
+        <v>0.0003443040768615901</v>
+      </c>
+      <c r="CK14" t="n">
+        <v>6.666365516139194e-05</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>0.000113522881292738</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>0.0001225947344209999</v>
+      </c>
+      <c r="CN14" t="n">
+        <v>0.001202412648126483</v>
+      </c>
+      <c r="CO14" t="n">
+        <v>0.0007492030854336917</v>
+      </c>
+      <c r="CP14" t="n">
+        <v>0.001361679402180016</v>
+      </c>
+      <c r="CQ14" t="n">
+        <v>0.0001273518137168139</v>
+      </c>
+      <c r="CR14" t="n">
+        <v>0.0005427669966593385</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>0.0001891328865895048</v>
+      </c>
+      <c r="CT14" t="n">
+        <v>0.000433766923379153</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>0.0003101833281107247</v>
+      </c>
+      <c r="CV14" t="n">
+        <v>3.64422558050137e-05</v>
+      </c>
+      <c r="CW14" t="n">
+        <v>0.0004259115958120674</v>
+      </c>
+      <c r="CX14" t="n">
+        <v>2.170243533328176e-05</v>
+      </c>
+      <c r="CY14" t="n">
+        <v>0.0003799529804382473</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>0.0002607779751997441</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>0.0007723140879534185</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>0.000115537695819512</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>6.014415703248233e-06</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>3.538795499480329e-05</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>9.562766354065388e-05</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>0.0006051207310520113</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.0005424095434136689</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>0.0001067485791281797</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.001326406723819673</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>0.0006436067051254213</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>2.851023054972757e-05</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.000860390136949718</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>0.0003449922660365701</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.0001594937930349261</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>0.0001688979973550886</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>0.0001508664718130603</v>
+      </c>
+      <c r="DQ14" t="n">
+        <v>0.0004907536786049604</v>
+      </c>
+      <c r="DR14" t="n">
+        <v>9.381439303979278e-05</v>
+      </c>
+      <c r="DS14" t="n">
+        <v>1.462356158299372e-05</v>
+      </c>
+      <c r="DT14" t="n">
+        <v>0.000341603095876053</v>
+      </c>
+      <c r="DU14" t="n">
+        <v>0.0009469275828450918</v>
+      </c>
+      <c r="DV14" t="n">
+        <v>9.224560926668346e-06</v>
+      </c>
+      <c r="DW14" t="n">
+        <v>0.0001891119900392368</v>
+      </c>
+      <c r="DX14" t="n">
+        <v>0.0001462401996832341</v>
+      </c>
+      <c r="DY14" t="n">
+        <v>5.93015065533109e-05</v>
+      </c>
+      <c r="DZ14" t="n">
+        <v>0.0008973493240773678</v>
+      </c>
+      <c r="EA14" t="n">
+        <v>0.0005656343419104815</v>
+      </c>
+      <c r="EB14" t="n">
+        <v>0.0004563828406389803</v>
+      </c>
+      <c r="EC14" t="n">
+        <v>1.202605199068785e-05</v>
+      </c>
+      <c r="ED14" t="n">
+        <v>0.0004026626993436366</v>
+      </c>
+      <c r="EE14" t="n">
+        <v>0.001052219537086785</v>
+      </c>
+      <c r="EF14" t="n">
+        <v>8.991852519102395e-05</v>
+      </c>
+      <c r="EG14" t="n">
+        <v>0.0001187128073070198</v>
+      </c>
+      <c r="EH14" t="n">
+        <v>0.0002200455346610397</v>
+      </c>
+      <c r="EI14" t="n">
+        <v>8.123068255372345e-06</v>
+      </c>
+      <c r="EJ14" t="n">
+        <v>0.0002516734239179641</v>
+      </c>
+      <c r="EK14" t="n">
+        <v>0.0007589306915178895</v>
+      </c>
+      <c r="EL14" t="n">
+        <v>0.0003976040752604604</v>
+      </c>
+      <c r="EM14" t="n">
+        <v>0.0001133587211370468</v>
+      </c>
+      <c r="EN14" t="n">
+        <v>7.004113285802305e-05</v>
+      </c>
+      <c r="EO14" t="n">
+        <v>8.149160566972569e-05</v>
+      </c>
+      <c r="EP14" t="n">
+        <v>0.000336057273671031</v>
+      </c>
+      <c r="EQ14" t="n">
+        <v>0.0004224443109706044</v>
+      </c>
+      <c r="ER14" t="n">
+        <v>0.0004231402417644858</v>
+      </c>
+      <c r="ES14" t="n">
+        <v>0.0002627750800456852</v>
+      </c>
+      <c r="ET14" t="n">
+        <v>0.0005982236471027136</v>
+      </c>
+      <c r="EU14" t="n">
+        <v>0.0002614635450299829</v>
+      </c>
+      <c r="EV14" t="n">
+        <v>6.57061900710687e-06</v>
+      </c>
+      <c r="EW14" t="n">
+        <v>0.0004270656791049987</v>
+      </c>
+      <c r="EX14" t="n">
+        <v>6.592184217879549e-05</v>
+      </c>
+      <c r="EY14" t="n">
+        <v>0.0006660750368610024</v>
+      </c>
+      <c r="EZ14" t="n">
+        <v>5.220435923547484e-05</v>
+      </c>
+      <c r="FA14" t="n">
+        <v>0.0004751027445308864</v>
+      </c>
+      <c r="FB14" t="n">
+        <v>0.000232933511142619</v>
+      </c>
+      <c r="FC14" t="n">
+        <v>0.0006404441082850099</v>
+      </c>
+      <c r="FD14" t="n">
+        <v>0.000268771720584482</v>
+      </c>
+      <c r="FE14" t="n">
+        <v>3.526583168422803e-05</v>
+      </c>
+      <c r="FF14" t="n">
+        <v>4.530721344053745e-05</v>
+      </c>
+      <c r="FG14" t="n">
+        <v>3.340675903018564e-05</v>
+      </c>
+      <c r="FH14" t="n">
+        <v>0.000717054819688201</v>
+      </c>
+      <c r="FI14" t="n">
+        <v>0.0004835640429519117</v>
+      </c>
+      <c r="FJ14" t="n">
+        <v>0.000174675282323733</v>
+      </c>
+      <c r="FK14" t="n">
+        <v>0.0004219749243929982</v>
+      </c>
+      <c r="FL14" t="n">
+        <v>0.0003776688827201724</v>
+      </c>
+      <c r="FM14" t="n">
+        <v>0.0005058222450315952</v>
+      </c>
+      <c r="FN14" t="n">
+        <v>0.0003806327003985643</v>
+      </c>
+      <c r="FO14" t="n">
+        <v>0.0007915031164884567</v>
+      </c>
+      <c r="FP14" t="n">
+        <v>0.0001435676676919684</v>
+      </c>
+      <c r="FQ14" t="n">
+        <v>7.255254604388028e-05</v>
+      </c>
+      <c r="FR14" t="n">
+        <v>0.001126178191043437</v>
+      </c>
+      <c r="FS14" t="n">
+        <v>0.0007504777750000358</v>
+      </c>
+      <c r="FT14" t="n">
+        <v>0.001252345973625779</v>
+      </c>
+      <c r="FU14" t="n">
+        <v>0.0003392496146261692</v>
+      </c>
+      <c r="FV14" t="n">
+        <v>0.0001599866955075413</v>
+      </c>
+      <c r="FW14" t="n">
+        <v>0.0007989222649484873</v>
+      </c>
+      <c r="FX14" t="n">
+        <v>0.0005645205965265632</v>
+      </c>
+      <c r="FY14" t="n">
+        <v>0.0002286383823957294</v>
+      </c>
+      <c r="FZ14" t="n">
+        <v>0.0006741058314219117</v>
+      </c>
+      <c r="GA14" t="n">
+        <v>0.00065283861476928</v>
+      </c>
+      <c r="GB14" t="n">
+        <v>5.94256998738274e-05</v>
+      </c>
+      <c r="GC14" t="n">
+        <v>0.001045188750140369</v>
+      </c>
+      <c r="GD14" t="n">
+        <v>0.001015847665257752</v>
+      </c>
+      <c r="GE14" t="n">
+        <v>0.0001591596810612828</v>
+      </c>
+      <c r="GF14" t="n">
+        <v>0.0004889054107479751</v>
+      </c>
+      <c r="GG14" t="n">
+        <v>0.0004382500192150474</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>0</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="CZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ER15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES15" t="n">
+        <v>0</v>
+      </c>
+      <c r="ET15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="EZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="FZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="GG15" t="n">
         <v>0</v>
       </c>
     </row>
